--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Ultra Short Term Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Ultra Short Term Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="283">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Ultra Short Term Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -64,12 +64,18 @@
     <t>Government Securities</t>
   </si>
   <si>
+    <t>IN0020210160</t>
+  </si>
+  <si>
+    <t>SOV</t>
+  </si>
+  <si>
+    <t>State Government of Andhra Pradesh</t>
+  </si>
+  <si>
     <t>IN1020150042</t>
   </si>
   <si>
-    <t>SOV</t>
-  </si>
-  <si>
     <t>Non-Convertible debentures / Bonds</t>
   </si>
   <si>
@@ -82,517 +88,592 @@
     <t>CRISIL AAA</t>
   </si>
   <si>
+    <t>NABARD</t>
+  </si>
+  <si>
+    <t>INE261F08DX0</t>
+  </si>
+  <si>
+    <t>INE261F08DO9</t>
+  </si>
+  <si>
+    <t>Bharti Telecom Ltd. **</t>
+  </si>
+  <si>
+    <t>INE403D08181</t>
+  </si>
+  <si>
+    <t>CRISIL AA+</t>
+  </si>
+  <si>
+    <t>Larsen &amp; Toubro Ltd. **</t>
+  </si>
+  <si>
+    <t>INE018A08BK6</t>
+  </si>
+  <si>
+    <t>INE115A07QB9</t>
+  </si>
+  <si>
+    <t>Oberoi Realty Ltd. **</t>
+  </si>
+  <si>
+    <t>INE093I07066</t>
+  </si>
+  <si>
+    <t>CARE AA+</t>
+  </si>
+  <si>
+    <t>Motilal Oswal Home Finance Ltd **</t>
+  </si>
+  <si>
+    <t>INE658R07430</t>
+  </si>
+  <si>
+    <t>ICRA AA</t>
+  </si>
+  <si>
+    <t>INE261F08DT8</t>
+  </si>
+  <si>
+    <t>Mankind Pharma Ltd **</t>
+  </si>
+  <si>
+    <t>INE634S07017</t>
+  </si>
+  <si>
+    <t>DLF Cyber City Developers Ltd. **</t>
+  </si>
+  <si>
+    <t>INE186K07098</t>
+  </si>
+  <si>
+    <t>ICRA AA+</t>
+  </si>
+  <si>
+    <t>Tata Housing Development Company Ltd. **</t>
+  </si>
+  <si>
+    <t>INE582L08052</t>
+  </si>
+  <si>
+    <t>CARE AA</t>
+  </si>
+  <si>
+    <t>LIC Housing Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE115A07QE3</t>
+  </si>
+  <si>
     <t>Small Industries Development Bank Of India. **</t>
   </si>
   <si>
-    <t>INE556F08JU6</t>
-  </si>
-  <si>
-    <t>CARE AAA</t>
-  </si>
-  <si>
-    <t>Bharti Telecom Ltd. **</t>
-  </si>
-  <si>
-    <t>INE403D08181</t>
-  </si>
-  <si>
-    <t>CRISIL AA+</t>
-  </si>
-  <si>
-    <t>NABARD</t>
-  </si>
-  <si>
-    <t>INE261F08DX0</t>
-  </si>
-  <si>
-    <t>INE556F08JZ5</t>
+    <t>INE556F08KI9</t>
+  </si>
+  <si>
+    <t>INE403D08132</t>
+  </si>
+  <si>
+    <t>INE403D08157</t>
+  </si>
+  <si>
+    <t>L&amp;T Metro Rail (Hyderabad) Ltd. **</t>
+  </si>
+  <si>
+    <t>INE128M08078</t>
+  </si>
+  <si>
+    <t>CRISIL AAA(CE)</t>
+  </si>
+  <si>
+    <t>Summit Digitel Infrastructure Ltd **</t>
+  </si>
+  <si>
+    <t>INE507T07062</t>
+  </si>
+  <si>
+    <t>INE115A07PV9</t>
+  </si>
+  <si>
+    <t>INE115A07QZ8</t>
+  </si>
+  <si>
+    <t>INE115A07QT1</t>
+  </si>
+  <si>
+    <t>Shriram Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE721A07SB0</t>
+  </si>
+  <si>
+    <t>Tata Realty &amp; Infrastructure Ltd. **</t>
+  </si>
+  <si>
+    <t>INE371K08219</t>
+  </si>
+  <si>
+    <t>Export-Import Bank Of India **</t>
+  </si>
+  <si>
+    <t>INE514E08EU9</t>
+  </si>
+  <si>
+    <t>Nirma Ltd. **</t>
+  </si>
+  <si>
+    <t>INE091A07216</t>
+  </si>
+  <si>
+    <t>CRISIL AA</t>
+  </si>
+  <si>
+    <t>UNO Minda Ltd. **</t>
+  </si>
+  <si>
+    <t>INE405E08044</t>
+  </si>
+  <si>
+    <t>Mahindra Rural Housing Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE950O08287</t>
+  </si>
+  <si>
+    <t>Motilal oswal finvest Ltd **</t>
+  </si>
+  <si>
+    <t>INE01WN07094</t>
+  </si>
+  <si>
+    <t>NABARD **</t>
+  </si>
+  <si>
+    <t>INE261F08DR2</t>
   </si>
   <si>
     <t>ICRA AAA</t>
   </si>
   <si>
-    <t>L&amp;T Metro Rail (Hyderabad) Ltd. **</t>
-  </si>
-  <si>
-    <t>INE128M08060</t>
-  </si>
-  <si>
-    <t>CRISIL AAA(CE)</t>
+    <t>Power Finance Corporation Ltd. **</t>
+  </si>
+  <si>
+    <t>INE134E08JE9</t>
+  </si>
+  <si>
+    <t>Muthoot Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE414G07HU2</t>
   </si>
   <si>
     <t>Rural Electrification Corporation Ltd. **</t>
   </si>
   <si>
-    <t>INE020B08906</t>
-  </si>
-  <si>
-    <t>INE115A07QB9</t>
-  </si>
-  <si>
-    <t>Power Finance Corporation Ltd. **</t>
-  </si>
-  <si>
-    <t>INE134E08KT5</t>
-  </si>
-  <si>
-    <t>Oberoi Realty Ltd. **</t>
-  </si>
-  <si>
-    <t>INE093I07066</t>
-  </si>
-  <si>
-    <t>CARE AA+</t>
-  </si>
-  <si>
-    <t>Motilal Oswal Home Finance Ltd **</t>
-  </si>
-  <si>
-    <t>INE658R07430</t>
-  </si>
-  <si>
-    <t>ICRA AA</t>
-  </si>
-  <si>
-    <t>INE556F08KA6</t>
-  </si>
-  <si>
-    <t>Mankind Pharma Ltd **</t>
-  </si>
-  <si>
-    <t>INE634S07017</t>
-  </si>
-  <si>
-    <t>DLF Cyber City Developers Ltd. **</t>
-  </si>
-  <si>
-    <t>INE186K07098</t>
-  </si>
-  <si>
-    <t>ICRA AA+</t>
-  </si>
-  <si>
-    <t>Tata Housing Development Company Ltd. **</t>
-  </si>
-  <si>
-    <t>INE582L08052</t>
-  </si>
-  <si>
-    <t>CARE AA</t>
-  </si>
-  <si>
-    <t>INE556F08JV4</t>
-  </si>
-  <si>
-    <t>INE261F08DO9</t>
-  </si>
-  <si>
-    <t>Nirma Ltd.</t>
-  </si>
-  <si>
-    <t>INE091A07190</t>
-  </si>
-  <si>
-    <t>CRISIL AA</t>
-  </si>
-  <si>
-    <t>INE115A07QE3</t>
-  </si>
-  <si>
-    <t>INE134E08MN4</t>
+    <t>INE020B08DF6</t>
+  </si>
+  <si>
+    <t>INE582L08060</t>
+  </si>
+  <si>
+    <t>INE261F08EF5</t>
+  </si>
+  <si>
+    <t>INE950O08303</t>
+  </si>
+  <si>
+    <t>INE020B08EW9</t>
+  </si>
+  <si>
+    <t>INE414G07JB8</t>
+  </si>
+  <si>
+    <t>INE020B08FC8</t>
+  </si>
+  <si>
+    <t>Manappuram Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE522D07CH7</t>
+  </si>
+  <si>
+    <t>INE261F08EA6</t>
+  </si>
+  <si>
+    <t>INE721A07RR8</t>
+  </si>
+  <si>
+    <t>Aavas Financiers Ltd. **</t>
+  </si>
+  <si>
+    <t>INE216P07258</t>
+  </si>
+  <si>
+    <t>INE405E08051</t>
+  </si>
+  <si>
+    <t>Aditya Birla Real Estate Ltd. **</t>
+  </si>
+  <si>
+    <t>INE055A08037</t>
+  </si>
+  <si>
+    <t>DLF Home Developers Ltd. **</t>
+  </si>
+  <si>
+    <t>INE351E07018</t>
+  </si>
+  <si>
+    <t>Bahadur Chand Investments Pvt. Ltd. **</t>
+  </si>
+  <si>
+    <t>INE087M08134</t>
+  </si>
+  <si>
+    <t>INE950O07362</t>
+  </si>
+  <si>
+    <t>FITCH AA+</t>
+  </si>
+  <si>
+    <t>INE020B08AH8</t>
+  </si>
+  <si>
+    <t>INE721A07RH9</t>
+  </si>
+  <si>
+    <t>Power Finance Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE134E08LP1</t>
+  </si>
+  <si>
+    <t>INE020B08DK6</t>
+  </si>
+  <si>
+    <t>INE261F08EI9</t>
+  </si>
+  <si>
+    <t>INE414G07JF9</t>
+  </si>
+  <si>
+    <t>INE403D08207</t>
+  </si>
+  <si>
+    <t>INE414G07JI3</t>
+  </si>
+  <si>
+    <t>INE414G07IR6</t>
+  </si>
+  <si>
+    <t>INE556F08KJ7</t>
+  </si>
+  <si>
+    <t>INE134E08ML8</t>
+  </si>
+  <si>
+    <t>INE020B08ET5</t>
+  </si>
+  <si>
+    <t>Titan Company Ltd. **</t>
+  </si>
+  <si>
+    <t>INE280A08015</t>
+  </si>
+  <si>
+    <t>INE134E08LO4</t>
+  </si>
+  <si>
+    <t>EMBASSY OFFICE PARKS REIT **</t>
+  </si>
+  <si>
+    <t>INE041007084</t>
+  </si>
+  <si>
+    <t>INE020B08FF1</t>
+  </si>
+  <si>
+    <t>INE414G07JH5</t>
+  </si>
+  <si>
+    <t>INE634S07025</t>
+  </si>
+  <si>
+    <t>Kotak Mahindra Investments Ltd. **</t>
+  </si>
+  <si>
+    <t>INE975F07IO5</t>
+  </si>
+  <si>
+    <t>Tata Capital Housing Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE033L07IC6</t>
+  </si>
+  <si>
+    <t>Zero Coupon Bonds / Deep Discount Bonds</t>
+  </si>
+  <si>
+    <t>Nil</t>
+  </si>
+  <si>
+    <t>Privately Placed/unlisted</t>
+  </si>
+  <si>
+    <t>Securitized Debt Instruments</t>
+  </si>
+  <si>
+    <t>Term Deposits</t>
+  </si>
+  <si>
+    <t>Deposits (maturity not exceeding 91 days)</t>
+  </si>
+  <si>
+    <t>Deposits (Placed as Margin)</t>
+  </si>
+  <si>
+    <t>Money Market Instruments</t>
+  </si>
+  <si>
+    <t>Certificate of Deposits</t>
+  </si>
+  <si>
+    <t>IndusInd Bank Ltd. **</t>
+  </si>
+  <si>
+    <t>INE095A16Y84</t>
+  </si>
+  <si>
+    <t>CRISIL A1+</t>
+  </si>
+  <si>
+    <t>Punjab National Bank **</t>
+  </si>
+  <si>
+    <t>INE160A16QT8</t>
+  </si>
+  <si>
+    <t>INE095A16Z18</t>
+  </si>
+  <si>
+    <t>INE261F16900</t>
+  </si>
+  <si>
+    <t>Indian Bank **</t>
+  </si>
+  <si>
+    <t>INE562A16NX4</t>
+  </si>
+  <si>
+    <t>HDFC Bank Ltd. **</t>
+  </si>
+  <si>
+    <t>INE040A16GS5</t>
   </si>
   <si>
     <t>Small Industries Development Bank Of India.</t>
   </si>
   <si>
-    <t>INE556F08KI9</t>
-  </si>
-  <si>
-    <t>INE115A07PZ0</t>
-  </si>
-  <si>
-    <t>Summit Digitel Infrastructure Ltd **</t>
-  </si>
-  <si>
-    <t>INE507T07062</t>
-  </si>
-  <si>
-    <t>Godrej Industries Ltd. **</t>
-  </si>
-  <si>
-    <t>INE233A08097</t>
-  </si>
-  <si>
-    <t>Tata Realty &amp; Infrastructure Ltd. **</t>
-  </si>
-  <si>
-    <t>INE371K08219</t>
-  </si>
-  <si>
-    <t>INE091A07216</t>
-  </si>
-  <si>
-    <t>Shriram Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE721A07RI7</t>
-  </si>
-  <si>
-    <t>Motilal oswal finvest Ltd **</t>
-  </si>
-  <si>
-    <t>INE01WN07094</t>
-  </si>
-  <si>
-    <t>INE115A07QT1</t>
-  </si>
-  <si>
-    <t>INE371K08227</t>
-  </si>
-  <si>
-    <t>INE115A07PQ9</t>
-  </si>
-  <si>
-    <t>INE261F08DR2</t>
-  </si>
-  <si>
-    <t>NABARD **</t>
-  </si>
-  <si>
-    <t>INE261F08DK7</t>
-  </si>
-  <si>
-    <t>INE556F08JY8</t>
-  </si>
-  <si>
-    <t>INE582L08060</t>
-  </si>
-  <si>
-    <t>INE261F08DQ4</t>
-  </si>
-  <si>
-    <t>Aditya Birla Real Estate Ltd. **</t>
-  </si>
-  <si>
-    <t>INE055A08037</t>
-  </si>
-  <si>
-    <t>DLF Home Developers Ltd. **</t>
-  </si>
-  <si>
-    <t>INE351E07018</t>
-  </si>
-  <si>
-    <t>Aavas Financiers Ltd. **</t>
-  </si>
-  <si>
-    <t>INE216P07258</t>
-  </si>
-  <si>
-    <t>INE721A07SB0</t>
-  </si>
-  <si>
-    <t>INE403D08132</t>
-  </si>
-  <si>
-    <t>Manappuram Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE522D07CH7</t>
-  </si>
-  <si>
-    <t>INE721A07RR8</t>
-  </si>
-  <si>
-    <t>INE261F08DT8</t>
-  </si>
-  <si>
-    <t>Mahindra Rural Housing Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE950O07362</t>
-  </si>
-  <si>
-    <t>FITCH AA+</t>
-  </si>
-  <si>
-    <t>Power Finance Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE134E08LO4</t>
-  </si>
-  <si>
-    <t>Shriram Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE721A07RH9</t>
-  </si>
-  <si>
-    <t>INE020B08DK6</t>
-  </si>
-  <si>
-    <t>INE634S07025</t>
-  </si>
-  <si>
-    <t>Motilal Oswal Home Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE658R08180</t>
-  </si>
-  <si>
-    <t>FITCH AA</t>
-  </si>
-  <si>
-    <t>INE403D08207</t>
-  </si>
-  <si>
-    <t>INE261F08DM3</t>
-  </si>
-  <si>
-    <t>INE020B08ET5</t>
-  </si>
-  <si>
-    <t>LIC Housing Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE115A07PW7</t>
-  </si>
-  <si>
-    <t>INE261F08EA6</t>
-  </si>
-  <si>
-    <t>INE128M08078</t>
-  </si>
-  <si>
-    <t>EMBASSY OFFICE PARKS REIT **</t>
-  </si>
-  <si>
-    <t>INE041007084</t>
-  </si>
-  <si>
-    <t>Tata Steel Ltd. **</t>
-  </si>
-  <si>
-    <t>INE081A08231</t>
-  </si>
-  <si>
-    <t>Kotak Mahindra Investments Ltd.</t>
-  </si>
-  <si>
-    <t>INE975F07IO5</t>
-  </si>
-  <si>
-    <t>Tata Capital Housing Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE033L07IC6</t>
-  </si>
-  <si>
-    <t>Zero Coupon Bonds / Deep Discount Bonds</t>
-  </si>
-  <si>
-    <t>Nil</t>
-  </si>
-  <si>
-    <t>Privately Placed/unlisted</t>
-  </si>
-  <si>
-    <t>Securitized Debt Instruments</t>
-  </si>
-  <si>
-    <t>FIRST BUSINESS RECEIVABLES TRUST **</t>
-  </si>
-  <si>
-    <t>INE0BTV15212</t>
-  </si>
-  <si>
-    <t>CRISIL AAA(SO)</t>
-  </si>
-  <si>
-    <t>Term Deposits</t>
-  </si>
-  <si>
-    <t>Deposits (maturity not exceeding 91 days)</t>
-  </si>
-  <si>
-    <t>Deposits (Placed as Margin)</t>
-  </si>
-  <si>
-    <t>Money Market Instruments</t>
-  </si>
-  <si>
-    <t>Certificate of Deposits</t>
-  </si>
-  <si>
-    <t>RBL Bank Ltd. **</t>
-  </si>
-  <si>
-    <t>INE976G16NV7</t>
+    <t>INE556F16AX2</t>
+  </si>
+  <si>
+    <t>Bank Of Baroda **</t>
+  </si>
+  <si>
+    <t>INE028A16HJ7</t>
+  </si>
+  <si>
+    <t>FITCH A1+</t>
+  </si>
+  <si>
+    <t>INE556F16AZ7</t>
+  </si>
+  <si>
+    <t>INE556F16BH3</t>
+  </si>
+  <si>
+    <t>INE514E16CL5</t>
+  </si>
+  <si>
+    <t>IDFC First Bank Ltd. **</t>
+  </si>
+  <si>
+    <t>INE092T16YI0</t>
+  </si>
+  <si>
+    <t>INE040A16FY5</t>
+  </si>
+  <si>
+    <t>IDBI Bank Ltd. **</t>
+  </si>
+  <si>
+    <t>INE008A16X57</t>
+  </si>
+  <si>
+    <t>INE556F16BC4</t>
+  </si>
+  <si>
+    <t>INE556F16BI1</t>
+  </si>
+  <si>
+    <t>Bank Of India **</t>
+  </si>
+  <si>
+    <t>INE084A16CZ7</t>
+  </si>
+  <si>
+    <t>INE028A16HW0</t>
+  </si>
+  <si>
+    <t>Axis Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE238AD6892</t>
+  </si>
+  <si>
+    <t>AU Small Finance Bank Ltd. **</t>
+  </si>
+  <si>
+    <t>INE949L16CX3</t>
+  </si>
+  <si>
+    <t>INE949L16DA9</t>
+  </si>
+  <si>
+    <t>INE949L16DC5</t>
+  </si>
+  <si>
+    <t>Punjab National Bank</t>
+  </si>
+  <si>
+    <t>INE160A16QL5</t>
+  </si>
+  <si>
+    <t>INE040A16GF2</t>
+  </si>
+  <si>
+    <t>Canara Bank **</t>
+  </si>
+  <si>
+    <t>INE476A16B23</t>
+  </si>
+  <si>
+    <t>INE160A16RK5</t>
+  </si>
+  <si>
+    <t>INE160A16RP4</t>
+  </si>
+  <si>
+    <t>INE261F16AA7</t>
+  </si>
+  <si>
+    <t>INE949L16DP7</t>
+  </si>
+  <si>
+    <t>Equitas Small Finance Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE063P16AT6</t>
+  </si>
+  <si>
+    <t>INE556F16BD2</t>
+  </si>
+  <si>
+    <t>INE238AD6900</t>
+  </si>
+  <si>
+    <t>Canara Bank</t>
+  </si>
+  <si>
+    <t>INE476A16ZQ5</t>
+  </si>
+  <si>
+    <t>INE476A16ZT9</t>
+  </si>
+  <si>
+    <t>INE949L16DO0</t>
+  </si>
+  <si>
+    <t>INE476A16A24</t>
+  </si>
+  <si>
+    <t>INE238AD6918</t>
+  </si>
+  <si>
+    <t>Commercial Papers</t>
+  </si>
+  <si>
+    <t>Torrent Electricals Ltd **</t>
+  </si>
+  <si>
+    <t>INE0B5U14017</t>
+  </si>
+  <si>
+    <t>Angel One Ltd. **</t>
+  </si>
+  <si>
+    <t>INE732I14AS8</t>
+  </si>
+  <si>
+    <t>JM Financial Services Ltd. **</t>
+  </si>
+  <si>
+    <t>INE012I14QX1</t>
+  </si>
+  <si>
+    <t>JSW Energy Ltd **</t>
+  </si>
+  <si>
+    <t>INE121E14359</t>
   </si>
   <si>
     <t>ICRA A1+</t>
   </si>
   <si>
-    <t>Punjab National Bank **</t>
-  </si>
-  <si>
-    <t>INE160A16QT8</t>
-  </si>
-  <si>
-    <t>CRISIL A1+</t>
-  </si>
-  <si>
-    <t>INE261F16900</t>
-  </si>
-  <si>
-    <t>IndusInd Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE095A16V46</t>
-  </si>
-  <si>
-    <t>Indian Bank **</t>
-  </si>
-  <si>
-    <t>INE562A16NX4</t>
-  </si>
-  <si>
-    <t>INE562A16MZ1</t>
-  </si>
-  <si>
-    <t>AU Small Finance Bank Ltd. **</t>
-  </si>
-  <si>
-    <t>INE949L16CS3</t>
-  </si>
-  <si>
-    <t>INE160A16QL5</t>
-  </si>
-  <si>
-    <t>Bank Of Baroda **</t>
-  </si>
-  <si>
-    <t>INE028A16HJ7</t>
-  </si>
-  <si>
-    <t>FITCH A1+</t>
-  </si>
-  <si>
-    <t>Punjab National Bank</t>
-  </si>
-  <si>
-    <t>INE160A16PK9</t>
-  </si>
-  <si>
-    <t>The Federal Bank Ltd. **</t>
-  </si>
-  <si>
-    <t>INE171A16ME6</t>
-  </si>
-  <si>
-    <t>IDBI Bank Ltd. **</t>
-  </si>
-  <si>
-    <t>INE008A16X57</t>
-  </si>
-  <si>
-    <t>INE261F16785</t>
-  </si>
-  <si>
-    <t>Bank Of India **</t>
-  </si>
-  <si>
-    <t>INE084A16CZ7</t>
-  </si>
-  <si>
-    <t>INE160A16PE2</t>
-  </si>
-  <si>
-    <t>HDFC Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE040A16FA5</t>
-  </si>
-  <si>
-    <t>Axis Bank Ltd. **</t>
-  </si>
-  <si>
-    <t>INE238AD6892</t>
-  </si>
-  <si>
-    <t>INE949L16CX3</t>
-  </si>
-  <si>
-    <t>INE949L16DA9</t>
-  </si>
-  <si>
-    <t>INE949L16DC5</t>
-  </si>
-  <si>
-    <t>INE095A16V61</t>
-  </si>
-  <si>
-    <t>Commercial Papers</t>
-  </si>
-  <si>
-    <t>JM Financial Services Ltd. **</t>
-  </si>
-  <si>
-    <t>INE012I14QX1</t>
-  </si>
-  <si>
-    <t>Export-Import Bank Of India **</t>
-  </si>
-  <si>
     <t>INE514E14SO0</t>
   </si>
   <si>
+    <t>INE732I14BE6</t>
+  </si>
+  <si>
     <t>INE012I14QY9</t>
   </si>
   <si>
-    <t>Bahadur Chand Investments Pvt. Ltd. **</t>
-  </si>
-  <si>
-    <t>INE087M14BM0</t>
-  </si>
-  <si>
-    <t>Birla Group Holdings Pvt. Ltd. **</t>
-  </si>
-  <si>
-    <t>INE09OL14EZ0</t>
+    <t>Nuvama Wealth &amp; Investment Ltd **</t>
+  </si>
+  <si>
+    <t>INE523L14773</t>
+  </si>
+  <si>
+    <t>INE523L14740</t>
+  </si>
+  <si>
+    <t>INE523L14781</t>
   </si>
   <si>
     <t>Sharekhan Ltd **</t>
   </si>
   <si>
-    <t>INE211H14856</t>
-  </si>
-  <si>
-    <t>Nuvama Wealth &amp; Investment Ltd **</t>
-  </si>
-  <si>
-    <t>INE523L14740</t>
-  </si>
-  <si>
-    <t>INE523L14781</t>
-  </si>
-  <si>
     <t>INE211H14831</t>
   </si>
   <si>
-    <t>INE523L14773</t>
-  </si>
-  <si>
-    <t>PVR Inox Ltd. **</t>
-  </si>
-  <si>
-    <t>INE191H14488</t>
-  </si>
-  <si>
-    <t>IGH Holdings Pvt Ltd. **</t>
-  </si>
-  <si>
-    <t>INE02FN14317</t>
+    <t>Aadhar Housing Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE883F14112</t>
+  </si>
+  <si>
+    <t>Phoenix ARC PVT LTD. **</t>
+  </si>
+  <si>
+    <t>INE163K14176</t>
+  </si>
+  <si>
+    <t>INE163K14184</t>
+  </si>
+  <si>
+    <t>INE211H14955</t>
   </si>
   <si>
     <t>PVR INOX Ltd. **</t>
@@ -601,34 +682,40 @@
     <t>INE191H14504</t>
   </si>
   <si>
-    <t>INE211H14955</t>
-  </si>
-  <si>
     <t>INE211H14948</t>
   </si>
   <si>
+    <t>PVR Inox Ltd **</t>
+  </si>
+  <si>
+    <t>INE191H14512</t>
+  </si>
+  <si>
+    <t>INE883F14104</t>
+  </si>
+  <si>
+    <t>Indostar Capital Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE896L14ES7</t>
+  </si>
+  <si>
+    <t>INE896L14ER9</t>
+  </si>
+  <si>
     <t>Bills Rediscounted</t>
   </si>
   <si>
     <t>Treasury Bills</t>
   </si>
   <si>
-    <t>364 Days Treasury Bills</t>
-  </si>
-  <si>
-    <t>IN002023Z471</t>
-  </si>
-  <si>
-    <t>IN002023Z539</t>
-  </si>
-  <si>
-    <t>IN002023Z489</t>
-  </si>
-  <si>
     <t>182 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002024Y241</t>
+    <t>IN002024Y480</t>
+  </si>
+  <si>
+    <t>IN002024Y498</t>
   </si>
   <si>
     <t>Units of an Alternative Investment Fund (AIF)</t>
@@ -655,13 +742,55 @@
     <t xml:space="preserve">INTEREST RATE SWAPS (At Notional Value) </t>
   </si>
   <si>
+    <t> Hongkong and Shanghai Banking Corporation Ltd.- MD -03-Oct-2025 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> DBS Bank India Ltd- MD -11-Mar-2027 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> BNP Paribas- MD -29-Jan-2027 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> BNP Paribas- MD -16-Jan-2026 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -16-Jan-2026 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Nomura Fixed Income Securities Ltd- MD -08-Mar-2027 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -16-Feb-2026 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> DBS Bank India Ltd- MD -16-Feb-2026 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -29-Dec-2025 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> BNP Paribas- MD -29-Dec-2025 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Hongkong and Shanghai Banking Corporation Ltd.- MD -08-Oct-2025 (Pay fixed/receive float)</t>
+  </si>
+  <si>
     <t> Barclays Bank- MD -06-Aug-2025 (Pay fixed/receive float)</t>
   </si>
   <si>
     <t> BNP Paribas- MD -06-Aug-2025 (Pay fixed/receive float)</t>
   </si>
   <si>
-    <t> Nomura Fixed Income Securities Ltd- MD -06-Feb-2025 (Pay fixed/receive float)</t>
+    <t> Barclays Bank- MD -17-Feb-2027 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Hongkong and Shanghai Banking Corporation Ltd.- MD -20-Mar-2026 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> DBS Bank India Ltd- MD -25-May-2026 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -25-May-2026 (Pay fixed/receive float)</t>
   </si>
   <si>
     <t> ICICI Securities Primary Dealership Ltd.- MD -10-Oct-2025 (Pay fixed/receive float)</t>
@@ -670,39 +799,42 @@
     <t> Barclays Bank- MD -06-Jan-2027 (Pay fixed/receive float)</t>
   </si>
   <si>
-    <t> Standard Chartered Bank- MD -19-Feb-2025 (Pay fixed/receive float)</t>
-  </si>
-  <si>
-    <t> Hongkong and Shanghai Banking Corporation Ltd.- MD -08-Oct-2025 (Pay fixed/receive float)</t>
+    <t> Nomura Fixed Income Securities Ltd- MD -07-May-2027 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Hongkong and Shanghai Banking Corporation Ltd.- MD -09-Mar-2026 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> DBS Bank India Ltd- MD -26-Feb-2027 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t>GSCCIL- MD -30-Apr-2027 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Hongkong and Shanghai Banking Corporation Ltd.- MD -26-Feb-2027 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t>GSCCIL- MD -07-May-2027 (Pay fixed/receive float)</t>
   </si>
   <si>
     <t> ICICI Securities Primary Dealership Ltd.- MD -04-Dec-2025 (Pay fixed/receive float)</t>
   </si>
   <si>
-    <t> Standard Chartered Bank- MD -17-Feb-2025 (Pay fixed/receive float)</t>
-  </si>
-  <si>
-    <t> Hongkong and Shanghai Banking Corporation Ltd.- MD -03-Oct-2025 (Pay fixed/receive float)</t>
-  </si>
-  <si>
-    <t> BNP Paribas- MD -29-Jan-2027 (Pay fixed/receive float)</t>
-  </si>
-  <si>
-    <t> BNP Paribas- MD -16-Jan-2026 (Pay fixed/receive float)</t>
-  </si>
-  <si>
-    <t> Barclays Bank- MD -16-Jan-2026 (Pay fixed/receive float)</t>
-  </si>
-  <si>
-    <t> Barclays Bank- MD -29-Dec-2025 (Pay fixed/receive float)</t>
-  </si>
-  <si>
-    <t> BNP Paribas- MD -29-Dec-2025 (Pay fixed/receive float)</t>
+    <t> ICICI Securities Primary Dealership Ltd.- MD -06-Feb-2027 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -21-Oct-2026 (Pay fixed/receive float)</t>
   </si>
   <si>
     <t> Standard Chartered Bank- MD -25-Jan-2027 (Pay fixed/receive float)</t>
   </si>
   <si>
+    <t> BNP Paribas- MD -11-Mar-2027 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -25-Mar-2027 (Pay fixed/receive float)</t>
+  </si>
+  <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
@@ -718,7 +850,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -731,9 +863,6 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - NIFTY Ultra Short Duration Debt Index A-I</t>
   </si>
 </sst>
 </file>
@@ -1122,13 +1251,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>178</xdr:row>
+      <xdr:row>222</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>188</xdr:row>
+      <xdr:row>232</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1146,8 +1275,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="34842450"/>
-          <a:ext cx="6381750" cy="1905000"/>
+          <a:off x="666750" y="43233975"/>
+          <a:ext cx="6400800" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1161,13 +1290,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>193</xdr:row>
+      <xdr:row>237</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>203</xdr:row>
+      <xdr:row>247</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1185,8 +1314,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="37699950"/>
-          <a:ext cx="6381750" cy="1905000"/>
+          <a:off x="666750" y="46091475"/>
+          <a:ext cx="6400800" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1519,15 +1648,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J192"/>
+  <dimension ref="B1:J235"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="23" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="23" width="95.71428571428571" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="23" width="17.0" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="23" width="96.0" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="23" width="17.142857142857142" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="23" width="9.714285714285714" collapsed="true"/>
     <col min="5" max="5" bestFit="true" customWidth="true" style="23" width="19.714285714285715" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="23" width="11.142857142857142" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="23" width="12.285714285714286" collapsed="true"/>
     <col min="7" max="7" bestFit="true" customWidth="true" style="23" width="38.714285714285715" collapsed="true"/>
     <col min="8" max="8" bestFit="true" customWidth="true" style="23" width="11.714285714285714" collapsed="true"/>
     <col min="9" max="9" bestFit="true" customWidth="true" style="23" width="29.714285714285715" collapsed="true"/>
@@ -1619,10 +1748,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>704169.5099999998</v>
+        <v>770156.20</v>
       </c>
       <c r="H5" s="10">
-        <v>0.5097809801696</v>
+        <v>0.4734004787118997</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1656,10 +1785,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>694086.6199999998</v>
+        <v>770156.20</v>
       </c>
       <c r="H7" s="10">
-        <v>0.5024815082752</v>
+        <v>0.4734004787118997</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1693,10 +1822,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="9">
-        <v>7556.72</v>
+        <v>112197.61</v>
       </c>
       <c r="H9" s="10">
-        <v>0.0054706602228</v>
+        <v>0.0689657530312</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>13</v>
@@ -1713,22 +1842,22 @@
         <v>16</v>
       </c>
       <c r="D10" s="14">
-        <v>8.31</v>
+        <v>7.11</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F10" s="15">
-        <v>7500000</v>
+        <v>103500000</v>
       </c>
       <c r="G10" s="16">
-        <v>7556.72</v>
+        <v>104668.62</v>
       </c>
       <c r="H10" s="17">
-        <v>0.0054706602228</v>
+        <v>0.064337824995</v>
       </c>
       <c r="I10" s="16">
-        <v>6.82</v>
+        <v>6.84</v>
       </c>
       <c r="J10" s="11" t="s">
         <v>13</v>
@@ -1736,35 +1865,35 @@
     </row>
     <row r="11" spans="2:10" ht="15" customHeight="1">
       <c r="B11" s="12" t="s">
-        <v>13</v>
+        <v>18</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="14">
+        <v>8.31</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="15">
+        <v>7500000</v>
+      </c>
+      <c r="G11" s="16">
+        <v>7528.99</v>
+      </c>
+      <c r="H11" s="17">
+        <v>0.0046279280362</v>
+      </c>
+      <c r="I11" s="16">
+        <v>5.81</v>
       </c>
       <c r="J11" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="15" customHeight="1">
-      <c r="B12" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="9">
-        <v>686529.8999999998</v>
-      </c>
-      <c r="H12" s="10">
-        <v>0.4970108480524</v>
-      </c>
-      <c r="I12" s="9" t="s">
+      <c r="B12" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J12" s="11" t="s">
@@ -1772,29 +1901,29 @@
       </c>
     </row>
     <row r="13" spans="2:10" ht="15" customHeight="1">
-      <c r="B13" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="13" t="s">
+      <c r="B13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="14">
-        <v>7.82</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" s="15">
-        <v>4350</v>
-      </c>
-      <c r="G13" s="16">
-        <v>43458.33</v>
-      </c>
-      <c r="H13" s="17">
-        <v>0.0314615014559</v>
-      </c>
-      <c r="I13" s="16">
-        <v>7.84</v>
+      <c r="C13" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="9">
+        <v>657958.5900000001</v>
+      </c>
+      <c r="H13" s="10">
+        <v>0.40443472568069994</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J13" s="11" t="s">
         <v>13</v>
@@ -1802,28 +1931,28 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1">
       <c r="B14" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="D14" s="14">
+        <v>7.82</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="14">
-        <v>5.59</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>24</v>
-      </c>
       <c r="F14" s="15">
-        <v>3750</v>
+        <v>6000</v>
       </c>
       <c r="G14" s="16">
-        <v>37455.64</v>
+        <v>60231.30</v>
       </c>
       <c r="H14" s="17">
-        <v>0.0271158756535</v>
+        <v>0.0370230431874</v>
       </c>
       <c r="I14" s="16">
-        <v>7.38</v>
+        <v>6.75</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>13</v>
@@ -1831,28 +1960,28 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1">
       <c r="B15" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>26</v>
-      </c>
       <c r="D15" s="14">
-        <v>8.90</v>
+        <v>7.58</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F15" s="15">
-        <v>32500</v>
+        <v>38000</v>
       </c>
       <c r="G15" s="16">
-        <v>32599.13</v>
+        <v>38383.53</v>
       </c>
       <c r="H15" s="17">
-        <v>0.0236000227334</v>
+        <v>0.0235936313656</v>
       </c>
       <c r="I15" s="16">
-        <v>8.39</v>
+        <v>6.62</v>
       </c>
       <c r="J15" s="11" t="s">
         <v>13</v>
@@ -1860,28 +1989,28 @@
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1">
       <c r="B16" s="12" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D16" s="14">
-        <v>7.58</v>
+        <v>7.40</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F16" s="15">
-        <v>30500</v>
+        <v>3750</v>
       </c>
       <c r="G16" s="16">
-        <v>30457.97</v>
+        <v>37652.29</v>
       </c>
       <c r="H16" s="17">
-        <v>0.0220499376644</v>
+        <v>0.0231441519405</v>
       </c>
       <c r="I16" s="16">
-        <v>7.63</v>
+        <v>6.60</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>13</v>
@@ -1889,28 +2018,28 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1">
       <c r="B17" s="12" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D17" s="14">
-        <v>7.15</v>
+        <v>8.90</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F17" s="15">
-        <v>3000</v>
+        <v>34500</v>
       </c>
       <c r="G17" s="16">
-        <v>29878.56</v>
+        <v>34668.33</v>
       </c>
       <c r="H17" s="17">
-        <v>0.021630475882</v>
+        <v>0.0213099680535</v>
       </c>
       <c r="I17" s="16">
-        <v>7.75</v>
+        <v>7.58</v>
       </c>
       <c r="J17" s="11" t="s">
         <v>13</v>
@@ -1918,28 +2047,28 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D18" s="14">
-        <v>6.37</v>
+        <v>7.66</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F18" s="15">
-        <v>3000</v>
+        <v>25000</v>
       </c>
       <c r="G18" s="16">
-        <v>29869.86</v>
+        <v>25088.35</v>
       </c>
       <c r="H18" s="17">
-        <v>0.0216241775484</v>
+        <v>0.0154213351787</v>
       </c>
       <c r="I18" s="16">
-        <v>7.83</v>
+        <v>6.56</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>13</v>
@@ -1947,28 +2076,28 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
       <c r="B19" s="12" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D19" s="14">
-        <v>8.27</v>
+        <v>7.7201</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F19" s="15">
-        <v>2350</v>
+        <v>2250</v>
       </c>
       <c r="G19" s="16">
-        <v>23500.78</v>
+        <v>22630.10</v>
       </c>
       <c r="H19" s="17">
-        <v>0.0170133050254</v>
+        <v>0.0139102953055</v>
       </c>
       <c r="I19" s="16">
-        <v>7.58</v>
+        <v>6.70</v>
       </c>
       <c r="J19" s="11" t="s">
         <v>13</v>
@@ -1976,28 +2105,28 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1">
       <c r="B20" s="12" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D20" s="14">
-        <v>7.7201</v>
+        <v>7.95</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F20" s="15">
-        <v>2250</v>
+        <v>20000</v>
       </c>
       <c r="G20" s="16">
-        <v>22480.92</v>
+        <v>20234.86</v>
       </c>
       <c r="H20" s="17">
-        <v>0.0162749810521</v>
+        <v>0.0124379864899</v>
       </c>
       <c r="I20" s="16">
-        <v>7.80</v>
+        <v>7.26</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>13</v>
@@ -2005,28 +2134,28 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="14">
+        <v>8.55</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" s="14">
-        <v>7.17</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>21</v>
-      </c>
       <c r="F21" s="15">
-        <v>2250</v>
+        <v>20000</v>
       </c>
       <c r="G21" s="16">
-        <v>22442.11</v>
+        <v>20221.98</v>
       </c>
       <c r="H21" s="17">
-        <v>0.0162468846924</v>
+        <v>0.012430069397</v>
       </c>
       <c r="I21" s="16">
-        <v>7.66</v>
+        <v>7.74</v>
       </c>
       <c r="J21" s="11" t="s">
         <v>13</v>
@@ -2034,28 +2163,28 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
       <c r="B22" s="12" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D22" s="14">
-        <v>7.95</v>
+        <v>7.50</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="F22" s="15">
-        <v>20000</v>
+        <v>1750</v>
       </c>
       <c r="G22" s="16">
-        <v>20006.70</v>
+        <v>17561.16</v>
       </c>
       <c r="H22" s="17">
-        <v>0.0144837783959</v>
+        <v>0.0107945135685</v>
       </c>
       <c r="I22" s="16">
-        <v>8.18</v>
+        <v>6.60</v>
       </c>
       <c r="J22" s="11" t="s">
         <v>13</v>
@@ -2063,28 +2192,28 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1">
       <c r="B23" s="12" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D23" s="14">
-        <v>8.55</v>
+        <v>7.99</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F23" s="15">
-        <v>20000</v>
+        <v>15500</v>
       </c>
       <c r="G23" s="16">
-        <v>19983.58</v>
+        <v>15630.03</v>
       </c>
       <c r="H23" s="17">
-        <v>0.0144670407552</v>
+        <v>0.0096074844094</v>
       </c>
       <c r="I23" s="16">
-        <v>8.59</v>
+        <v>7.09</v>
       </c>
       <c r="J23" s="11" t="s">
         <v>13</v>
@@ -2092,28 +2221,28 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1">
       <c r="B24" s="12" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D24" s="14">
-        <v>7.25</v>
+        <v>8.40</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F24" s="15">
-        <v>1600</v>
+        <v>15000</v>
       </c>
       <c r="G24" s="16">
-        <v>15940.02</v>
+        <v>15243.80</v>
       </c>
       <c r="H24" s="17">
-        <v>0.0115397200591</v>
+        <v>0.0093700761188</v>
       </c>
       <c r="I24" s="16">
-        <v>7.75</v>
+        <v>7.38</v>
       </c>
       <c r="J24" s="11" t="s">
         <v>13</v>
@@ -2121,28 +2250,28 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
       <c r="B25" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="14">
+        <v>8.217500000000001</v>
+      </c>
+      <c r="E25" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="14">
-        <v>7.99</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>27</v>
-      </c>
       <c r="F25" s="15">
-        <v>15500</v>
+        <v>15000</v>
       </c>
       <c r="G25" s="16">
-        <v>15513.86</v>
+        <v>15069.15</v>
       </c>
       <c r="H25" s="17">
-        <v>0.0112312030622</v>
+        <v>0.0092627220605</v>
       </c>
       <c r="I25" s="16">
-        <v>8.05</v>
+        <v>7.08</v>
       </c>
       <c r="J25" s="11" t="s">
         <v>13</v>
@@ -2150,28 +2279,28 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>50</v>
-      </c>
       <c r="D26" s="14">
-        <v>8.40</v>
+        <v>7.82</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F26" s="15">
-        <v>15000</v>
+        <v>1350</v>
       </c>
       <c r="G26" s="16">
-        <v>15034.61</v>
+        <v>13574.09</v>
       </c>
       <c r="H26" s="17">
-        <v>0.0108842517511</v>
+        <v>0.0083437368992</v>
       </c>
       <c r="I26" s="16">
-        <v>8.3</v>
+        <v>6.70</v>
       </c>
       <c r="J26" s="11" t="s">
         <v>13</v>
@@ -2179,28 +2308,28 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
       <c r="B27" s="12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D27" s="14">
-        <v>8.217500000000001</v>
+        <v>7.44</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="F27" s="15">
-        <v>15000</v>
+        <v>12500</v>
       </c>
       <c r="G27" s="16">
-        <v>14996.72</v>
+        <v>12616.01</v>
       </c>
       <c r="H27" s="17">
-        <v>0.0108568214221</v>
+        <v>0.0077548232079</v>
       </c>
       <c r="I27" s="16">
-        <v>8.16</v>
+        <v>6.61</v>
       </c>
       <c r="J27" s="11" t="s">
         <v>13</v>
@@ -2208,28 +2337,28 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1">
       <c r="B28" s="12" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D28" s="14">
-        <v>5.57</v>
+        <v>8.8</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F28" s="15">
-        <v>1500</v>
+        <v>1250</v>
       </c>
       <c r="G28" s="16">
-        <v>14972.28</v>
+        <v>12550.01</v>
       </c>
       <c r="H28" s="17">
-        <v>0.0108391281721</v>
+        <v>0.0077142542537</v>
       </c>
       <c r="I28" s="16">
-        <v>7.45</v>
+        <v>7.58</v>
       </c>
       <c r="J28" s="11" t="s">
         <v>13</v>
@@ -2237,28 +2366,28 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D29" s="14">
-        <v>7.40</v>
+        <v>8.700000000000001</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F29" s="15">
-        <v>1500</v>
+        <v>1250</v>
       </c>
       <c r="G29" s="16">
-        <v>14954.60</v>
+        <v>12549.55</v>
       </c>
       <c r="H29" s="17">
-        <v>0.0108263287998</v>
+        <v>0.0077139715004</v>
       </c>
       <c r="I29" s="16">
-        <v>7.72</v>
+        <v>7.58</v>
       </c>
       <c r="J29" s="11" t="s">
         <v>13</v>
@@ -2266,28 +2395,28 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D30" s="14">
-        <v>8.3</v>
+        <v>6.58</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F30" s="15">
-        <v>14500</v>
+        <v>1250</v>
       </c>
       <c r="G30" s="16">
-        <v>14502.15</v>
+        <v>12471.63</v>
       </c>
       <c r="H30" s="17">
-        <v>0.0104987792521</v>
+        <v>0.0076660755472</v>
       </c>
       <c r="I30" s="16">
-        <v>7.80</v>
+        <v>6.81</v>
       </c>
       <c r="J30" s="11" t="s">
         <v>13</v>
@@ -2295,28 +2424,28 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D31" s="14">
-        <v>7.82</v>
+        <v>6.59</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F31" s="15">
-        <v>1350</v>
+        <v>1200</v>
       </c>
       <c r="G31" s="16">
-        <v>13494.60</v>
+        <v>11989.56</v>
       </c>
       <c r="H31" s="17">
-        <v>0.0097693670591</v>
+        <v>0.0073697562177</v>
       </c>
       <c r="I31" s="16">
-        <v>7.84</v>
+        <v>6.85</v>
       </c>
       <c r="J31" s="11" t="s">
         <v>13</v>
@@ -2324,28 +2453,28 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D32" s="14">
-        <v>7.44</v>
+        <v>7.90</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F32" s="15">
-        <v>12500</v>
+        <v>1000</v>
       </c>
       <c r="G32" s="16">
-        <v>12477.90</v>
+        <v>10205.46</v>
       </c>
       <c r="H32" s="17">
-        <v>0.0090333307565</v>
+        <v>0.0062731036243</v>
       </c>
       <c r="I32" s="16">
-        <v>7.70</v>
+        <v>6.79</v>
       </c>
       <c r="J32" s="11" t="s">
         <v>13</v>
@@ -2353,28 +2482,28 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
       <c r="B33" s="12" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D33" s="14">
-        <v>7.44</v>
+        <v>7.74</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F33" s="15">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="G33" s="16">
-        <v>12461.05</v>
+        <v>10186.36</v>
       </c>
       <c r="H33" s="17">
-        <v>0.0090211322597</v>
+        <v>0.0062613632148</v>
       </c>
       <c r="I33" s="16">
-        <v>7.61</v>
+        <v>6.85</v>
       </c>
       <c r="J33" s="11" t="s">
         <v>13</v>
@@ -2382,28 +2511,28 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D34" s="14">
-        <v>7.38</v>
+        <v>7.865</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F34" s="15">
-        <v>1250</v>
+        <v>10000</v>
       </c>
       <c r="G34" s="16">
-        <v>12454.20</v>
+        <v>10113.96</v>
       </c>
       <c r="H34" s="17">
-        <v>0.0090161732269</v>
+        <v>0.0062168603014</v>
       </c>
       <c r="I34" s="16">
-        <v>7.82</v>
+        <v>6.82</v>
       </c>
       <c r="J34" s="11" t="s">
         <v>13</v>
@@ -2411,28 +2540,28 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D35" s="14">
-        <v>6.59</v>
+        <v>9.200000000000001</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F35" s="15">
-        <v>1100</v>
+        <v>10000</v>
       </c>
       <c r="G35" s="16">
-        <v>10847.88</v>
+        <v>10113.33</v>
       </c>
       <c r="H35" s="17">
-        <v>0.0078532836492</v>
+        <v>0.0062164730523</v>
       </c>
       <c r="I35" s="16">
-        <v>7.89</v>
+        <v>7.93</v>
       </c>
       <c r="J35" s="11" t="s">
         <v>13</v>
@@ -2440,28 +2569,28 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D36" s="14">
-        <v>7.17</v>
+        <v>8.25</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F36" s="15">
-        <v>1075</v>
+        <v>10000</v>
       </c>
       <c r="G36" s="16">
-        <v>10713.30</v>
+        <v>10081.04</v>
       </c>
       <c r="H36" s="17">
-        <v>0.007755854943</v>
+        <v>0.0061966249988</v>
       </c>
       <c r="I36" s="16">
-        <v>8.03</v>
+        <v>7.04</v>
       </c>
       <c r="J36" s="11" t="s">
         <v>13</v>
@@ -2469,28 +2598,28 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D37" s="14">
-        <v>8.25</v>
+        <v>8.18</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F37" s="15">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="G37" s="16">
-        <v>10021.94</v>
+        <v>10075.16</v>
       </c>
       <c r="H37" s="17">
-        <v>0.0072553473615</v>
+        <v>0.0061930106738</v>
       </c>
       <c r="I37" s="16">
-        <v>8.01</v>
+        <v>6.43</v>
       </c>
       <c r="J37" s="11" t="s">
         <v>13</v>
@@ -2498,28 +2627,28 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D38" s="14">
         <v>8.40</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F38" s="15">
         <v>10000</v>
       </c>
       <c r="G38" s="16">
-        <v>10017.82</v>
+        <v>10072.78</v>
       </c>
       <c r="H38" s="17">
-        <v>0.0072523647023</v>
+        <v>0.0061915477327</v>
       </c>
       <c r="I38" s="16">
-        <v>8.2</v>
+        <v>7.26</v>
       </c>
       <c r="J38" s="11" t="s">
         <v>13</v>
@@ -2527,28 +2656,28 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
       <c r="B39" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C39" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C39" s="13" t="s">
-        <v>73</v>
-      </c>
       <c r="D39" s="14">
-        <v>9.65</v>
+        <v>7.75</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F39" s="15">
         <v>10000</v>
       </c>
       <c r="G39" s="16">
-        <v>10016.40</v>
+        <v>10067.82</v>
       </c>
       <c r="H39" s="17">
-        <v>0.0072513366984</v>
+        <v>0.0061884989144</v>
       </c>
       <c r="I39" s="16">
-        <v>8.26</v>
+        <v>7.24</v>
       </c>
       <c r="J39" s="11" t="s">
         <v>13</v>
@@ -2556,28 +2685,28 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="C40" s="13" t="s">
-        <v>75</v>
-      </c>
       <c r="D40" s="14">
-        <v>9.50</v>
+        <v>8.315000000000001</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="F40" s="15">
         <v>10000</v>
       </c>
       <c r="G40" s="16">
-        <v>10013.91</v>
+        <v>10054.22</v>
       </c>
       <c r="H40" s="17">
-        <v>0.0072495340719</v>
+        <v>0.0061801392511</v>
       </c>
       <c r="I40" s="16">
-        <v>8.93</v>
+        <v>6.99</v>
       </c>
       <c r="J40" s="11" t="s">
         <v>13</v>
@@ -2585,28 +2714,28 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
       <c r="B41" s="12" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="C41" s="13" t="s">
         <v>76</v>
       </c>
       <c r="D41" s="14">
-        <v>7.865</v>
+        <v>9.50</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="F41" s="15">
         <v>10000</v>
       </c>
       <c r="G41" s="16">
-        <v>10008.22</v>
+        <v>10036.10</v>
       </c>
       <c r="H41" s="17">
-        <v>0.0072454148169</v>
+        <v>0.0061690012291</v>
       </c>
       <c r="I41" s="16">
-        <v>7.76</v>
+        <v>7.67</v>
       </c>
       <c r="J41" s="11" t="s">
         <v>13</v>
@@ -2614,28 +2743,28 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
       <c r="B42" s="12" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D42" s="14">
-        <v>8.10</v>
+        <v>7.20</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="F42" s="15">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="G42" s="16">
-        <v>10000.15</v>
+        <v>10011.43</v>
       </c>
       <c r="H42" s="17">
-        <v>0.0072395725694</v>
+        <v>0.0061538370458</v>
       </c>
       <c r="I42" s="16">
-        <v>7.69</v>
+        <v>6.50</v>
       </c>
       <c r="J42" s="11" t="s">
         <v>13</v>
@@ -2643,28 +2772,28 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
       <c r="B43" s="12" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D43" s="14">
-        <v>5.9943</v>
+        <v>7.30</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F43" s="15">
-        <v>1000</v>
+        <v>875</v>
       </c>
       <c r="G43" s="16">
-        <v>9980.96</v>
+        <v>8880.65</v>
       </c>
       <c r="H43" s="17">
-        <v>0.0072256800381</v>
+        <v>0.0054587679243</v>
       </c>
       <c r="I43" s="16">
-        <v>7.40</v>
+        <v>6.53</v>
       </c>
       <c r="J43" s="11" t="s">
         <v>13</v>
@@ -2672,28 +2801,28 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
       <c r="B44" s="12" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D44" s="14">
-        <v>7.20</v>
+        <v>8.65</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F44" s="15">
-        <v>1000</v>
+        <v>8500</v>
       </c>
       <c r="G44" s="16">
-        <v>9950.31</v>
+        <v>8545.72</v>
       </c>
       <c r="H44" s="17">
-        <v>0.007203491081</v>
+        <v>0.0052528927754</v>
       </c>
       <c r="I44" s="16">
-        <v>7.80</v>
+        <v>7.48</v>
       </c>
       <c r="J44" s="11" t="s">
         <v>13</v>
@@ -2701,28 +2830,28 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="12" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D45" s="14">
-        <v>5.70</v>
+        <v>5.85</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F45" s="15">
-        <v>1000</v>
+        <v>850</v>
       </c>
       <c r="G45" s="16">
-        <v>9889.57</v>
+        <v>8462.19</v>
       </c>
       <c r="H45" s="17">
-        <v>0.0071595185768</v>
+        <v>0.0052015484611</v>
       </c>
       <c r="I45" s="16">
-        <v>7.80</v>
+        <v>6.51</v>
       </c>
       <c r="J45" s="11" t="s">
         <v>13</v>
@@ -2730,28 +2859,28 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="12" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D46" s="14">
-        <v>7.15</v>
+        <v>8.05</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F46" s="15">
-        <v>950</v>
+        <v>7500</v>
       </c>
       <c r="G46" s="16">
-        <v>9471.72</v>
+        <v>7528.17</v>
       </c>
       <c r="H46" s="17">
-        <v>0.0068570175745</v>
+        <v>0.0046274239976</v>
       </c>
       <c r="I46" s="16">
-        <v>7.70</v>
+        <v>7.08</v>
       </c>
       <c r="J46" s="11" t="s">
         <v>13</v>
@@ -2759,28 +2888,28 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
       <c r="B47" s="12" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D47" s="14">
-        <v>8.05</v>
+        <v>7.80</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="F47" s="15">
-        <v>7500</v>
+        <v>5000</v>
       </c>
       <c r="G47" s="16">
-        <v>7489.58</v>
+        <v>5098.26</v>
       </c>
       <c r="H47" s="17">
-        <v>0.0054220544616</v>
+        <v>0.0031338041875</v>
       </c>
       <c r="I47" s="16">
-        <v>8.16</v>
+        <v>6.57</v>
       </c>
       <c r="J47" s="11" t="s">
         <v>13</v>
@@ -2788,28 +2917,28 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="12" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D48" s="14">
-        <v>7.25</v>
+        <v>8.315000000000001</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F48" s="15">
-        <v>750</v>
+        <v>5000</v>
       </c>
       <c r="G48" s="16">
-        <v>7469.71</v>
+        <v>5094.98</v>
       </c>
       <c r="H48" s="17">
-        <v>0.0054076696467</v>
+        <v>0.0031317880334</v>
       </c>
       <c r="I48" s="16">
-        <v>7.80</v>
+        <v>7.23</v>
       </c>
       <c r="J48" s="11" t="s">
         <v>13</v>
@@ -2817,28 +2946,28 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D49" s="14">
-        <v>8.10</v>
+        <v>7.71</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="F49" s="15">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="G49" s="16">
-        <v>5987.89</v>
+        <v>5092.73</v>
       </c>
       <c r="H49" s="17">
-        <v>0.0043349113956</v>
+        <v>0.0031304050009</v>
       </c>
       <c r="I49" s="16">
-        <v>8.24</v>
+        <v>6.52</v>
       </c>
       <c r="J49" s="11" t="s">
         <v>13</v>
@@ -2846,28 +2975,28 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
       <c r="B50" s="12" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D50" s="14">
-        <v>8.50</v>
+        <v>8.90</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F50" s="15">
         <v>5000</v>
       </c>
       <c r="G50" s="16">
-        <v>5012.43</v>
+        <v>5077.93</v>
       </c>
       <c r="H50" s="17">
-        <v>0.0036287306424</v>
+        <v>0.0031213077202</v>
       </c>
       <c r="I50" s="16">
-        <v>8.12</v>
+        <v>8.04</v>
       </c>
       <c r="J50" s="11" t="s">
         <v>13</v>
@@ -2875,28 +3004,28 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
       <c r="B51" s="12" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D51" s="14">
-        <v>8.42</v>
+        <v>7.70</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="F51" s="15">
         <v>5000</v>
       </c>
       <c r="G51" s="16">
-        <v>5010.32</v>
+        <v>5063.04</v>
       </c>
       <c r="H51" s="17">
-        <v>0.0036272031155</v>
+        <v>0.0031121551183</v>
       </c>
       <c r="I51" s="16">
-        <v>8.29</v>
+        <v>6.55</v>
       </c>
       <c r="J51" s="11" t="s">
         <v>13</v>
@@ -2904,28 +3033,28 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
       <c r="B52" s="12" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D52" s="14">
-        <v>9.200000000000001</v>
+        <v>9.10</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="F52" s="15">
         <v>5000</v>
       </c>
       <c r="G52" s="16">
-        <v>5009.98</v>
+        <v>5049.94</v>
       </c>
       <c r="H52" s="17">
-        <v>0.0036269569738</v>
+        <v>0.0031041027956</v>
       </c>
       <c r="I52" s="16">
-        <v>8.96</v>
+        <v>8.15</v>
       </c>
       <c r="J52" s="11" t="s">
         <v>13</v>
@@ -2933,28 +3062,28 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
       <c r="B53" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D53" s="14">
-        <v>8.8</v>
+        <v>7.50</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F53" s="15">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="G53" s="16">
-        <v>5009.95</v>
+        <v>5048.99</v>
       </c>
       <c r="H53" s="17">
-        <v>0.0036269352554</v>
+        <v>0.0031035188485</v>
       </c>
       <c r="I53" s="16">
-        <v>8.39</v>
+        <v>6.62</v>
       </c>
       <c r="J53" s="11" t="s">
         <v>13</v>
@@ -2962,28 +3091,28 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
       <c r="B54" s="12" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D54" s="14">
-        <v>9.10</v>
+        <v>8.75</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F54" s="15">
         <v>5000</v>
       </c>
       <c r="G54" s="16">
-        <v>4998.50</v>
+        <v>5045.02</v>
       </c>
       <c r="H54" s="17">
-        <v>0.0036186460691</v>
+        <v>0.0031010785644</v>
       </c>
       <c r="I54" s="16">
-        <v>9.05</v>
+        <v>7.96</v>
       </c>
       <c r="J54" s="11" t="s">
         <v>13</v>
@@ -2991,28 +3120,28 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
       <c r="B55" s="12" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D55" s="14">
-        <v>8.75</v>
+        <v>8.42</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F55" s="15">
         <v>5000</v>
       </c>
       <c r="G55" s="16">
-        <v>4994.83</v>
+        <v>5038</v>
       </c>
       <c r="H55" s="17">
-        <v>0.0036159891858</v>
+        <v>0.0030967635029</v>
       </c>
       <c r="I55" s="16">
-        <v>8.67</v>
+        <v>7.85</v>
       </c>
       <c r="J55" s="11" t="s">
         <v>13</v>
@@ -3020,28 +3149,28 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
       <c r="B56" s="12" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D56" s="14">
-        <v>7.50</v>
+        <v>7.75</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="F56" s="15">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="G56" s="16">
-        <v>4986.46</v>
+        <v>5034.59</v>
       </c>
       <c r="H56" s="17">
-        <v>0.0036099297545</v>
+        <v>0.0030946674403</v>
       </c>
       <c r="I56" s="16">
-        <v>7.75</v>
+        <v>7.23</v>
       </c>
       <c r="J56" s="11" t="s">
         <v>13</v>
@@ -3049,28 +3178,28 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1">
       <c r="B57" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D57" s="14">
-        <v>7.75</v>
+        <v>8.10</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="F57" s="15">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="G57" s="16">
-        <v>4985.15</v>
+        <v>5032.18</v>
       </c>
       <c r="H57" s="17">
-        <v>0.0036089813847</v>
+        <v>0.0030931860588</v>
       </c>
       <c r="I57" s="16">
-        <v>8.09</v>
+        <v>7.34</v>
       </c>
       <c r="J57" s="11" t="s">
         <v>13</v>
@@ -3078,28 +3207,28 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D58" s="14">
-        <v>7.13</v>
+        <v>8.50</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F58" s="15">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="G58" s="16">
-        <v>4977.32</v>
+        <v>5023.49</v>
       </c>
       <c r="H58" s="17">
-        <v>0.0036033128844</v>
+        <v>0.0030878444798</v>
       </c>
       <c r="I58" s="16">
-        <v>7.78</v>
+        <v>6.95</v>
       </c>
       <c r="J58" s="11" t="s">
         <v>13</v>
@@ -3107,28 +3236,28 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
       <c r="B59" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D59" s="14">
-        <v>8.75</v>
+        <v>9.25</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F59" s="15">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="G59" s="16">
-        <v>4489.34</v>
+        <v>5022.86</v>
       </c>
       <c r="H59" s="17">
-        <v>0.0032500415212</v>
+        <v>0.0030874572307</v>
       </c>
       <c r="I59" s="16">
-        <v>8.96</v>
+        <v>8.40</v>
       </c>
       <c r="J59" s="11" t="s">
         <v>13</v>
@@ -3136,28 +3265,28 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
       <c r="B60" s="12" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D60" s="14">
-        <v>5.94</v>
+        <v>7.75</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="F60" s="15">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G60" s="16">
-        <v>2950.64</v>
+        <v>5003.9</v>
       </c>
       <c r="H60" s="17">
-        <v>0.002136105199</v>
+        <v>0.0030758028766</v>
       </c>
       <c r="I60" s="16">
-        <v>7.72</v>
+        <v>6.65</v>
       </c>
       <c r="J60" s="11" t="s">
         <v>13</v>
@@ -3165,28 +3294,28 @@
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1">
       <c r="B61" s="12" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D61" s="14">
-        <v>7.99</v>
+        <v>7.95</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F61" s="15">
-        <v>2900</v>
+        <v>450</v>
       </c>
       <c r="G61" s="16">
-        <v>2905.12</v>
+        <v>4603.72</v>
       </c>
       <c r="H61" s="17">
-        <v>0.002103151159</v>
+        <v>0.0028298197844</v>
       </c>
       <c r="I61" s="16">
-        <v>8.02</v>
+        <v>6.52</v>
       </c>
       <c r="J61" s="11" t="s">
         <v>13</v>
@@ -3194,28 +3323,28 @@
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1">
       <c r="B62" s="12" t="s">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D62" s="14">
-        <v>7.266</v>
+        <v>8.75</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="F62" s="15">
-        <v>250</v>
+        <v>4500</v>
       </c>
       <c r="G62" s="16">
-        <v>2628.79</v>
+        <v>4535.98</v>
       </c>
       <c r="H62" s="17">
-        <v>0.0019031030509</v>
+        <v>0.0027881812851</v>
       </c>
       <c r="I62" s="16">
-        <v>8.74</v>
+        <v>7.92</v>
       </c>
       <c r="J62" s="11" t="s">
         <v>13</v>
@@ -3223,28 +3352,28 @@
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1">
       <c r="B63" s="12" t="s">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D63" s="14">
-        <v>8.950000000000001</v>
+        <v>7.13</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F63" s="15">
-        <v>2500</v>
+        <v>300</v>
       </c>
       <c r="G63" s="16">
-        <v>2523.63</v>
+        <v>3017.64</v>
       </c>
       <c r="H63" s="17">
-        <v>0.0018269728477</v>
+        <v>0.0018548863471</v>
       </c>
       <c r="I63" s="16">
-        <v>8.35</v>
+        <v>6.55</v>
       </c>
       <c r="J63" s="11" t="s">
         <v>13</v>
@@ -3252,28 +3381,28 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
       <c r="B64" s="12" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D64" s="14">
-        <v>5.96</v>
+        <v>5.94</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F64" s="15">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="G64" s="16">
-        <v>2499.37</v>
+        <v>2986.10</v>
       </c>
       <c r="H64" s="17">
-        <v>0.0018094099081</v>
+        <v>0.0018354993045</v>
       </c>
       <c r="I64" s="16">
-        <v>7.38</v>
+        <v>6.54</v>
       </c>
       <c r="J64" s="11" t="s">
         <v>13</v>
@@ -3281,28 +3410,28 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
       <c r="B65" s="12" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D65" s="14">
-        <v>7.79</v>
+        <v>7.70</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="F65" s="15">
         <v>2500</v>
       </c>
       <c r="G65" s="16">
-        <v>2499.34</v>
+        <v>2556.92</v>
       </c>
       <c r="H65" s="17">
-        <v>0.0018093881897</v>
+        <v>0.0015716904597</v>
       </c>
       <c r="I65" s="16">
-        <v>7.72</v>
+        <v>6.59</v>
       </c>
       <c r="J65" s="11" t="s">
         <v>13</v>
@@ -3310,28 +3439,28 @@
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
       <c r="B66" s="12" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="C66" s="13" t="s">
         <v>113</v>
       </c>
       <c r="D66" s="14">
-        <v>7.61</v>
+        <v>9.02</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F66" s="15">
-        <v>250</v>
+        <v>2500</v>
       </c>
       <c r="G66" s="16">
-        <v>2494.16</v>
+        <v>2545.36</v>
       </c>
       <c r="H66" s="17">
-        <v>0.0018056381474</v>
+        <v>0.0015645847459</v>
       </c>
       <c r="I66" s="16">
-        <v>7.80</v>
+        <v>8.04</v>
       </c>
       <c r="J66" s="11" t="s">
         <v>13</v>
@@ -3339,28 +3468,28 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
       <c r="B67" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C67" s="13" t="s">
         <v>114</v>
       </c>
       <c r="D67" s="14">
-        <v>7.50</v>
+        <v>8.950000000000001</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F67" s="15">
         <v>2500</v>
       </c>
       <c r="G67" s="16">
-        <v>2494.02</v>
+        <v>2544.97</v>
       </c>
       <c r="H67" s="17">
-        <v>0.0018055367949</v>
+        <v>0.0015643450202</v>
       </c>
       <c r="I67" s="16">
-        <v>7.62</v>
+        <v>7.59</v>
       </c>
       <c r="J67" s="11" t="s">
         <v>13</v>
@@ -3368,28 +3497,28 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="12" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="C68" s="13" t="s">
         <v>115</v>
       </c>
       <c r="D68" s="14">
-        <v>6.58</v>
+        <v>8.90</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F68" s="15">
-        <v>250</v>
+        <v>2500</v>
       </c>
       <c r="G68" s="16">
-        <v>2461.66</v>
+        <v>2542.75</v>
       </c>
       <c r="H68" s="17">
-        <v>0.0017821098894</v>
+        <v>0.0015629804281</v>
       </c>
       <c r="I68" s="16">
-        <v>7.89</v>
+        <v>8.04</v>
       </c>
       <c r="J68" s="11" t="s">
         <v>13</v>
@@ -3397,28 +3526,28 @@
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1">
       <c r="B69" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C69" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="C69" s="13" t="s">
-        <v>117</v>
-      </c>
       <c r="D69" s="14">
-        <v>7.05</v>
+        <v>8.78</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F69" s="15">
-        <v>150</v>
+        <v>2500</v>
       </c>
       <c r="G69" s="16">
-        <v>1483.48</v>
+        <v>2532.43</v>
       </c>
       <c r="H69" s="17">
-        <v>0.0010739600021</v>
+        <v>0.0015566369189</v>
       </c>
       <c r="I69" s="16">
-        <v>8.12</v>
+        <v>8.04</v>
       </c>
       <c r="J69" s="11" t="s">
         <v>13</v>
@@ -3426,28 +3555,28 @@
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1">
       <c r="B70" s="12" t="s">
-        <v>118</v>
+        <v>50</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D70" s="14">
-        <v>7.70</v>
+        <v>7.55</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>99</v>
+        <v>23</v>
       </c>
       <c r="F70" s="15">
-        <v>100</v>
+        <v>2500</v>
       </c>
       <c r="G70" s="16">
-        <v>999.47</v>
+        <v>2527.32</v>
       </c>
       <c r="H70" s="17">
-        <v>0.0007235627061</v>
+        <v>0.0015534958984</v>
       </c>
       <c r="I70" s="16">
-        <v>7.66</v>
+        <v>6.61</v>
       </c>
       <c r="J70" s="11" t="s">
         <v>13</v>
@@ -3455,28 +3584,28 @@
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1">
       <c r="B71" s="12" t="s">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D71" s="14">
-        <v>8.2185</v>
+        <v>7.55</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F71" s="15">
-        <v>150</v>
+        <v>2500</v>
       </c>
       <c r="G71" s="16">
-        <v>150.96</v>
+        <v>2526.59</v>
       </c>
       <c r="H71" s="17">
-        <v>0.0001092869482</v>
+        <v>0.0015530471812</v>
       </c>
       <c r="I71" s="16">
-        <v>7.80</v>
+        <v>6.55</v>
       </c>
       <c r="J71" s="11" t="s">
         <v>13</v>
@@ -3484,28 +3613,28 @@
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1">
       <c r="B72" s="12" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D72" s="14">
-        <v>7.8445</v>
+        <v>7.79</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="F72" s="15">
-        <v>150</v>
+        <v>2500</v>
       </c>
       <c r="G72" s="16">
-        <v>150.05</v>
+        <v>2512.29</v>
       </c>
       <c r="H72" s="17">
-        <v>0.0001086281569</v>
+        <v>0.0015442572411</v>
       </c>
       <c r="I72" s="16">
-        <v>7.80</v>
+        <v>6.51</v>
       </c>
       <c r="J72" s="11" t="s">
         <v>13</v>
@@ -3513,36 +3642,57 @@
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1">
       <c r="B73" s="12" t="s">
-        <v>13</v>
+        <v>120</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D73" s="14">
+        <v>7.75</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F73" s="15">
+        <v>2500</v>
+      </c>
+      <c r="G73" s="16">
+        <v>2508.3</v>
+      </c>
+      <c r="H73" s="17">
+        <v>0.0015418046634</v>
+      </c>
+      <c r="I73" s="16">
+        <v>6.65</v>
       </c>
       <c r="J73" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1">
-      <c r="B74" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F74" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G74" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="H74" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="I74" s="9" t="s">
-        <v>13</v>
+      <c r="B74" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D74" s="14">
+        <v>7.13</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F74" s="15">
+        <v>250</v>
+      </c>
+      <c r="G74" s="16">
+        <v>2502</v>
+      </c>
+      <c r="H74" s="17">
+        <v>0.0015379321723</v>
+      </c>
+      <c r="I74" s="16">
+        <v>6.33</v>
       </c>
       <c r="J74" s="11" t="s">
         <v>13</v>
@@ -3550,36 +3700,57 @@
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1">
       <c r="B75" s="12" t="s">
-        <v>13</v>
+        <v>123</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="D75" s="14">
+        <v>7.05</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F75" s="15">
+        <v>150</v>
+      </c>
+      <c r="G75" s="16">
+        <v>1499.24</v>
+      </c>
+      <c r="H75" s="17">
+        <v>0.0009215545284</v>
+      </c>
+      <c r="I75" s="16">
+        <v>7.29</v>
       </c>
       <c r="J75" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1">
-      <c r="B76" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D76" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E76" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F76" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G76" s="9" t="s">
+      <c r="B76" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C76" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="H76" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="I76" s="9" t="s">
-        <v>13</v>
+      <c r="D76" s="14">
+        <v>7.56</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F76" s="15">
+        <v>1250</v>
+      </c>
+      <c r="G76" s="16">
+        <v>1275.59</v>
+      </c>
+      <c r="H76" s="17">
+        <v>0.000784081095</v>
+      </c>
+      <c r="I76" s="16">
+        <v>6.53</v>
       </c>
       <c r="J76" s="11" t="s">
         <v>13</v>
@@ -3587,36 +3758,57 @@
     </row>
     <row r="77" spans="2:10" ht="15" customHeight="1">
       <c r="B77" s="12" t="s">
-        <v>13</v>
+        <v>82</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D77" s="14">
+        <v>8.97</v>
+      </c>
+      <c r="E77" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F77" s="15">
+        <v>500</v>
+      </c>
+      <c r="G77" s="16">
+        <v>506.50</v>
+      </c>
+      <c r="H77" s="17">
+        <v>0.0003113359893</v>
+      </c>
+      <c r="I77" s="16">
+        <v>8.04</v>
       </c>
       <c r="J77" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1">
-      <c r="B78" s="7" t="s">
+      <c r="B78" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C78" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="C78" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D78" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F78" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G78" s="9">
-        <v>10082.89</v>
-      </c>
-      <c r="H78" s="10">
-        <v>0.0072994718944</v>
-      </c>
-      <c r="I78" s="9" t="s">
-        <v>13</v>
+      <c r="D78" s="14">
+        <v>7.99</v>
+      </c>
+      <c r="E78" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F78" s="15">
+        <v>400</v>
+      </c>
+      <c r="G78" s="16">
+        <v>405.22</v>
+      </c>
+      <c r="H78" s="17">
+        <v>0.000249081085</v>
+      </c>
+      <c r="I78" s="16">
+        <v>7.09</v>
       </c>
       <c r="J78" s="11" t="s">
         <v>13</v>
@@ -3629,23 +3821,23 @@
       <c r="C79" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="D79" s="13" t="s">
-        <v>13</v>
+      <c r="D79" s="14">
+        <v>8.2185</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>130</v>
+        <v>23</v>
       </c>
       <c r="F79" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G79" s="16">
-        <v>10082.89</v>
+        <v>152.04</v>
       </c>
       <c r="H79" s="17">
-        <v>0.0072994718944</v>
+        <v>0.0000934561181</v>
       </c>
       <c r="I79" s="16">
-        <v>7.91</v>
+        <v>7.17</v>
       </c>
       <c r="J79" s="11" t="s">
         <v>13</v>
@@ -3653,35 +3845,35 @@
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1">
       <c r="B80" s="12" t="s">
-        <v>13</v>
+        <v>130</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D80" s="14">
+        <v>7.8445</v>
+      </c>
+      <c r="E80" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F80" s="15">
+        <v>150</v>
+      </c>
+      <c r="G80" s="16">
+        <v>151.60</v>
+      </c>
+      <c r="H80" s="17">
+        <v>0.0000931856584</v>
+      </c>
+      <c r="I80" s="16">
+        <v>6.97</v>
       </c>
       <c r="J80" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="81" spans="2:10" ht="15" customHeight="1">
-      <c r="B81" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="I81" s="9" t="s">
+      <c r="B81" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J81" s="11" t="s">
@@ -3689,7 +3881,28 @@
       </c>
     </row>
     <row r="82" spans="2:10" ht="15" customHeight="1">
-      <c r="B82" s="12" t="s">
+      <c r="B82" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G82" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="H82" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="I82" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J82" s="11" t="s">
@@ -3697,28 +3910,7 @@
       </c>
     </row>
     <row r="83" spans="2:10" ht="15" customHeight="1">
-      <c r="B83" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E83" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F83" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G83" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="I83" s="9" t="s">
+      <c r="B83" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J83" s="11" t="s">
@@ -3726,7 +3918,28 @@
       </c>
     </row>
     <row r="84" spans="2:10" ht="15" customHeight="1">
-      <c r="B84" s="12" t="s">
+      <c r="B84" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="H84" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="I84" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J84" s="11" t="s">
@@ -3734,36 +3947,36 @@
       </c>
     </row>
     <row r="85" spans="2:10" ht="15" customHeight="1">
-      <c r="B85" s="7" t="s">
+      <c r="B85" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J85" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" ht="15" customHeight="1">
+      <c r="B86" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="C85" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E85" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G85" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="I85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J85" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="86" spans="2:10" ht="15" customHeight="1">
-      <c r="B86" s="12" t="s">
+      <c r="H86" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="I86" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J86" s="11" t="s">
@@ -3771,28 +3984,7 @@
       </c>
     </row>
     <row r="87" spans="2:10" ht="15" customHeight="1">
-      <c r="B87" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D87" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E87" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F87" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G87" s="9">
-        <v>584084.2499999999</v>
-      </c>
-      <c r="H87" s="10">
-        <v>0.4228456887706001</v>
-      </c>
-      <c r="I87" s="9" t="s">
+      <c r="B87" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J87" s="11" t="s">
@@ -3800,7 +3992,28 @@
       </c>
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1">
-      <c r="B88" s="12" t="s">
+      <c r="B88" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F88" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G88" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="H88" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="I88" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J88" s="11" t="s">
@@ -3808,28 +4021,7 @@
       </c>
     </row>
     <row r="89" spans="2:10" ht="15" customHeight="1">
-      <c r="B89" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D89" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E89" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F89" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G89" s="9">
-        <v>340514.27999999985</v>
-      </c>
-      <c r="H89" s="10">
-        <v>0.24651408638879996</v>
-      </c>
-      <c r="I89" s="9" t="s">
+      <c r="B89" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J89" s="11" t="s">
@@ -3837,29 +4029,29 @@
       </c>
     </row>
     <row r="90" spans="2:10" ht="15" customHeight="1">
-      <c r="B90" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="C90" s="13" t="s">
+      <c r="B90" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="D90" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E90" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="F90" s="15">
-        <v>8000</v>
-      </c>
-      <c r="G90" s="16">
-        <v>39658.12</v>
-      </c>
-      <c r="H90" s="17">
-        <v>0.0287103531156</v>
-      </c>
-      <c r="I90" s="16">
-        <v>7.68</v>
+      <c r="C90" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G90" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="H90" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="I90" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J90" s="11" t="s">
         <v>13</v>
@@ -3867,57 +4059,36 @@
     </row>
     <row r="91" spans="2:10" ht="15" customHeight="1">
       <c r="B91" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="C91" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="D91" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E91" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="F91" s="15">
-        <v>6000</v>
-      </c>
-      <c r="G91" s="16">
-        <v>28007.46</v>
-      </c>
-      <c r="H91" s="17">
-        <v>0.0202758997772</v>
-      </c>
-      <c r="I91" s="16">
-        <v>7.62</v>
+        <v>13</v>
       </c>
       <c r="J91" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="92" spans="2:10" ht="15" customHeight="1">
-      <c r="B92" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="C92" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="D92" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E92" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="F92" s="15">
-        <v>5000</v>
-      </c>
-      <c r="G92" s="16">
-        <v>23275.03</v>
-      </c>
-      <c r="H92" s="17">
-        <v>0.0168498741261</v>
-      </c>
-      <c r="I92" s="16">
-        <v>7.62</v>
+      <c r="B92" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F92" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G92" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="H92" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="I92" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J92" s="11" t="s">
         <v>13</v>
@@ -3925,57 +4096,36 @@
     </row>
     <row r="93" spans="2:10" ht="15" customHeight="1">
       <c r="B93" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="C93" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="D93" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E93" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="F93" s="15">
-        <v>4500</v>
-      </c>
-      <c r="G93" s="16">
-        <v>22423.23</v>
-      </c>
-      <c r="H93" s="17">
-        <v>0.0162332165845</v>
-      </c>
-      <c r="I93" s="16">
-        <v>7.35</v>
+        <v>13</v>
       </c>
       <c r="J93" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="94" spans="2:10" ht="15" customHeight="1">
-      <c r="B94" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="C94" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="D94" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E94" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="F94" s="15">
-        <v>4500</v>
-      </c>
-      <c r="G94" s="16">
-        <v>20918.88</v>
-      </c>
-      <c r="H94" s="17">
-        <v>0.015144147821</v>
-      </c>
-      <c r="I94" s="16">
-        <v>7.60</v>
+      <c r="B94" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F94" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G94" s="9">
+        <v>808047.3099999998</v>
+      </c>
+      <c r="H94" s="10">
+        <v>0.4966914287991999</v>
+      </c>
+      <c r="I94" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J94" s="11" t="s">
         <v>13</v>
@@ -3983,57 +4133,36 @@
     </row>
     <row r="95" spans="2:10" ht="15" customHeight="1">
       <c r="B95" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="C95" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="D95" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E95" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="F95" s="15">
-        <v>4000</v>
-      </c>
-      <c r="G95" s="16">
-        <v>19548.78</v>
-      </c>
-      <c r="H95" s="17">
-        <v>0.0141522688614</v>
-      </c>
-      <c r="I95" s="16">
-        <v>7.59</v>
+        <v>13</v>
       </c>
       <c r="J95" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="96" spans="2:10" ht="15" customHeight="1">
-      <c r="B96" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="C96" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="D96" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E96" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="F96" s="15">
-        <v>4000</v>
-      </c>
-      <c r="G96" s="16">
-        <v>19141.56</v>
-      </c>
-      <c r="H96" s="17">
-        <v>0.0138574634093</v>
-      </c>
-      <c r="I96" s="16">
-        <v>7.99</v>
+      <c r="B96" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F96" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G96" s="9">
+        <v>496860.26</v>
+      </c>
+      <c r="H96" s="10">
+        <v>0.3054106231144</v>
+      </c>
+      <c r="I96" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J96" s="11" t="s">
         <v>13</v>
@@ -4041,28 +4170,28 @@
     </row>
     <row r="97" spans="2:10" ht="15" customHeight="1">
       <c r="B97" s="12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C97" s="13" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="D97" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F97" s="15">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="G97" s="16">
-        <v>18772.52</v>
+        <v>28950.96</v>
       </c>
       <c r="H97" s="17">
-        <v>0.0135902982307</v>
+        <v>0.0177956086353</v>
       </c>
       <c r="I97" s="16">
-        <v>7.63</v>
+        <v>6.82</v>
       </c>
       <c r="J97" s="11" t="s">
         <v>13</v>
@@ -4070,28 +4199,28 @@
     </row>
     <row r="98" spans="2:10" ht="15" customHeight="1">
       <c r="B98" s="12" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C98" s="13" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="D98" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="F98" s="15">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="G98" s="16">
-        <v>18674.14</v>
+        <v>28879.17</v>
       </c>
       <c r="H98" s="17">
-        <v>0.0135190763841</v>
+        <v>0.0177514806774</v>
       </c>
       <c r="I98" s="16">
-        <v>7.58</v>
+        <v>6.41</v>
       </c>
       <c r="J98" s="11" t="s">
         <v>13</v>
@@ -4099,28 +4228,28 @@
     </row>
     <row r="99" spans="2:10" ht="15" customHeight="1">
       <c r="B99" s="12" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C99" s="13" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="D99" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F99" s="15">
-        <v>3500</v>
+        <v>6000</v>
       </c>
       <c r="G99" s="16">
-        <v>17433.75</v>
+        <v>28570.89</v>
       </c>
       <c r="H99" s="17">
-        <v>0.0126211005118</v>
+        <v>0.0175619867805</v>
       </c>
       <c r="I99" s="16">
-        <v>7.30</v>
+        <v>6.81</v>
       </c>
       <c r="J99" s="11" t="s">
         <v>13</v>
@@ -4128,28 +4257,28 @@
     </row>
     <row r="100" spans="2:10" ht="15" customHeight="1">
       <c r="B100" s="12" t="s">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="D100" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F100" s="15">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="G100" s="16">
-        <v>14658.21</v>
+        <v>24007.68</v>
       </c>
       <c r="H100" s="17">
-        <v>0.010611758327</v>
+        <v>0.0147570677284</v>
       </c>
       <c r="I100" s="16">
-        <v>7.67</v>
+        <v>6.42</v>
       </c>
       <c r="J100" s="11" t="s">
         <v>13</v>
@@ -4157,28 +4286,28 @@
     </row>
     <row r="101" spans="2:10" ht="15" customHeight="1">
       <c r="B101" s="12" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="C101" s="13" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D101" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F101" s="15">
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="G101" s="16">
-        <v>13929.18</v>
+        <v>21577.75</v>
       </c>
       <c r="H101" s="17">
-        <v>0.0100839796846</v>
+        <v>0.0132634356246</v>
       </c>
       <c r="I101" s="16">
-        <v>7.73</v>
+        <v>6.42</v>
       </c>
       <c r="J101" s="11" t="s">
         <v>13</v>
@@ -4186,28 +4315,28 @@
     </row>
     <row r="102" spans="2:10" ht="15" customHeight="1">
       <c r="B102" s="12" t="s">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="C102" s="13" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="D102" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F102" s="15">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="G102" s="16">
-        <v>12485.01</v>
+        <v>21384.90</v>
       </c>
       <c r="H102" s="17">
-        <v>0.0090384780154</v>
+        <v>0.0131448943698</v>
       </c>
       <c r="I102" s="16">
-        <v>7.30</v>
+        <v>6.43</v>
       </c>
       <c r="J102" s="11" t="s">
         <v>13</v>
@@ -4215,28 +4344,28 @@
     </row>
     <row r="103" spans="2:10" ht="15" customHeight="1">
       <c r="B103" s="12" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C103" s="13" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D103" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F103" s="15">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="G103" s="16">
-        <v>11616.23</v>
+        <v>19357.84</v>
       </c>
       <c r="H103" s="17">
-        <v>0.0084095278639</v>
+        <v>0.0118988988505</v>
       </c>
       <c r="I103" s="16">
-        <v>7.65</v>
+        <v>6.48</v>
       </c>
       <c r="J103" s="11" t="s">
         <v>13</v>
@@ -4247,25 +4376,25 @@
         <v>154</v>
       </c>
       <c r="C104" s="13" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D104" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="F104" s="15">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="G104" s="16">
-        <v>9878.22</v>
+        <v>19251.20</v>
       </c>
       <c r="H104" s="17">
-        <v>0.0071513017852</v>
+        <v>0.0118333492554</v>
       </c>
       <c r="I104" s="16">
-        <v>7.50</v>
+        <v>6.40</v>
       </c>
       <c r="J104" s="11" t="s">
         <v>13</v>
@@ -4273,28 +4402,28 @@
     </row>
     <row r="105" spans="2:10" ht="15" customHeight="1">
       <c r="B105" s="12" t="s">
-        <v>164</v>
+        <v>50</v>
       </c>
       <c r="C105" s="13" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D105" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E105" s="13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F105" s="15">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="G105" s="16">
-        <v>9708.39</v>
+        <v>19161.88</v>
       </c>
       <c r="H105" s="17">
-        <v>0.0070283539684</v>
+        <v>0.0117784459374</v>
       </c>
       <c r="I105" s="16">
-        <v>7.67</v>
+        <v>6.44</v>
       </c>
       <c r="J105" s="11" t="s">
         <v>13</v>
@@ -4302,28 +4431,28 @@
     </row>
     <row r="106" spans="2:10" ht="15" customHeight="1">
       <c r="B106" s="12" t="s">
-        <v>166</v>
+        <v>50</v>
       </c>
       <c r="C106" s="13" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="D106" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E106" s="13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F106" s="15">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="G106" s="16">
-        <v>9565.27</v>
+        <v>18859.58</v>
       </c>
       <c r="H106" s="17">
-        <v>0.00692474276</v>
+        <v>0.0115926278336</v>
       </c>
       <c r="I106" s="16">
-        <v>7.68</v>
+        <v>6.53</v>
       </c>
       <c r="J106" s="11" t="s">
         <v>13</v>
@@ -4331,28 +4460,28 @@
     </row>
     <row r="107" spans="2:10" ht="15" customHeight="1">
       <c r="B107" s="12" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="C107" s="13" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="D107" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F107" s="15">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="G107" s="16">
-        <v>9498.10</v>
+        <v>18796.06</v>
       </c>
       <c r="H107" s="17">
-        <v>0.0068761152805</v>
+        <v>0.0115535832886</v>
       </c>
       <c r="I107" s="16">
-        <v>7.97</v>
+        <v>6.48</v>
       </c>
       <c r="J107" s="11" t="s">
         <v>13</v>
@@ -4360,28 +4489,28 @@
     </row>
     <row r="108" spans="2:10" ht="15" customHeight="1">
       <c r="B108" s="12" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="C108" s="13" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D108" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F108" s="15">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="G108" s="16">
-        <v>9433.54</v>
+        <v>18769.34</v>
       </c>
       <c r="H108" s="17">
-        <v>0.006829377301</v>
+        <v>0.011537159009</v>
       </c>
       <c r="I108" s="16">
-        <v>7.97</v>
+        <v>6.69</v>
       </c>
       <c r="J108" s="11" t="s">
         <v>13</v>
@@ -4389,28 +4518,28 @@
     </row>
     <row r="109" spans="2:10" ht="15" customHeight="1">
       <c r="B109" s="12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C109" s="13" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="D109" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F109" s="15">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G109" s="16">
-        <v>9398.69</v>
+        <v>14522.30</v>
       </c>
       <c r="H109" s="17">
-        <v>0.0068041477691</v>
+        <v>0.0089265836878</v>
       </c>
       <c r="I109" s="16">
-        <v>7.97</v>
+        <v>6.46</v>
       </c>
       <c r="J109" s="11" t="s">
         <v>13</v>
@@ -4418,28 +4547,28 @@
     </row>
     <row r="110" spans="2:10" ht="15" customHeight="1">
       <c r="B110" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="C110" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="D110" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E110" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="C110" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="D110" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E110" s="13" t="s">
-        <v>141</v>
-      </c>
       <c r="F110" s="15">
-        <v>500</v>
+        <v>3000</v>
       </c>
       <c r="G110" s="16">
-        <v>2489.97</v>
+        <v>14372.75</v>
       </c>
       <c r="H110" s="17">
-        <v>0.001802604812</v>
+        <v>0.0088346581257</v>
       </c>
       <c r="I110" s="16">
-        <v>7.35</v>
+        <v>6.56</v>
       </c>
       <c r="J110" s="11" t="s">
         <v>13</v>
@@ -4447,36 +4576,57 @@
     </row>
     <row r="111" spans="2:10" ht="15" customHeight="1">
       <c r="B111" s="12" t="s">
-        <v>13</v>
+        <v>50</v>
+      </c>
+      <c r="C111" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="D111" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E111" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F111" s="15">
+        <v>3000</v>
+      </c>
+      <c r="G111" s="16">
+        <v>14299.44</v>
+      </c>
+      <c r="H111" s="17">
+        <v>0.0087895958525</v>
+      </c>
+      <c r="I111" s="16">
+        <v>6.43</v>
       </c>
       <c r="J111" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="112" spans="2:10" ht="15" customHeight="1">
-      <c r="B112" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="C112" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D112" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E112" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F112" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G112" s="9">
-        <v>143973.73</v>
-      </c>
-      <c r="H112" s="10">
-        <v>0.10422926320419998</v>
-      </c>
-      <c r="I112" s="9" t="s">
-        <v>13</v>
+      <c r="B112" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C112" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="D112" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E112" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F112" s="15">
+        <v>3000</v>
+      </c>
+      <c r="G112" s="16">
+        <v>14108.99</v>
+      </c>
+      <c r="H112" s="17">
+        <v>0.0086725298325</v>
+      </c>
+      <c r="I112" s="16">
+        <v>6.53</v>
       </c>
       <c r="J112" s="11" t="s">
         <v>13</v>
@@ -4484,28 +4634,28 @@
     </row>
     <row r="113" spans="2:10" ht="15" customHeight="1">
       <c r="B113" s="12" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C113" s="13" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D113" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F113" s="15">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="G113" s="16">
-        <v>18982.9</v>
+        <v>11981.14</v>
       </c>
       <c r="H113" s="17">
-        <v>0.0137426020739</v>
+        <v>0.0073645806026</v>
       </c>
       <c r="I113" s="16">
-        <v>8.77</v>
+        <v>6.51</v>
       </c>
       <c r="J113" s="11" t="s">
         <v>13</v>
@@ -4513,28 +4663,28 @@
     </row>
     <row r="114" spans="2:10" ht="15" customHeight="1">
       <c r="B114" s="12" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="C114" s="13" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D114" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="F114" s="15">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="G114" s="16">
-        <v>18607.08</v>
+        <v>11920.30</v>
       </c>
       <c r="H114" s="17">
-        <v>0.0134705285387</v>
+        <v>0.007327183403</v>
       </c>
       <c r="I114" s="16">
-        <v>7.59</v>
+        <v>6.39</v>
       </c>
       <c r="J114" s="11" t="s">
         <v>13</v>
@@ -4542,28 +4692,28 @@
     </row>
     <row r="115" spans="2:10" ht="15" customHeight="1">
       <c r="B115" s="12" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C115" s="13" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D115" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F115" s="15">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="G115" s="16">
-        <v>16505.72</v>
+        <v>9837.76</v>
       </c>
       <c r="H115" s="17">
-        <v>0.0119492565363</v>
+        <v>0.006047085375</v>
       </c>
       <c r="I115" s="16">
-        <v>8.76</v>
+        <v>6.27</v>
       </c>
       <c r="J115" s="11" t="s">
         <v>13</v>
@@ -4571,28 +4721,28 @@
     </row>
     <row r="116" spans="2:10" ht="15" customHeight="1">
       <c r="B116" s="12" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C116" s="13" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D116" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="F116" s="15">
         <v>2000</v>
       </c>
       <c r="G116" s="16">
-        <v>9972.82</v>
+        <v>9778.72</v>
       </c>
       <c r="H116" s="17">
-        <v>0.0072197871144</v>
+        <v>0.0060107946014</v>
       </c>
       <c r="I116" s="16">
-        <v>8.29</v>
+        <v>6.77</v>
       </c>
       <c r="J116" s="11" t="s">
         <v>13</v>
@@ -4600,28 +4750,28 @@
     </row>
     <row r="117" spans="2:10" ht="15" customHeight="1">
       <c r="B117" s="12" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C117" s="13" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D117" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E117" s="13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F117" s="15">
         <v>2000</v>
       </c>
       <c r="G117" s="16">
-        <v>9898.60</v>
+        <v>9720.34</v>
       </c>
       <c r="H117" s="17">
-        <v>0.0071660558128</v>
+        <v>0.0059749095174</v>
       </c>
       <c r="I117" s="16">
-        <v>7.79</v>
+        <v>6.78</v>
       </c>
       <c r="J117" s="11" t="s">
         <v>13</v>
@@ -4629,28 +4779,28 @@
     </row>
     <row r="118" spans="2:10" ht="15" customHeight="1">
       <c r="B118" s="12" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C118" s="13" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="D118" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="F118" s="15">
         <v>2000</v>
       </c>
       <c r="G118" s="16">
-        <v>9745.52</v>
+        <v>9688.88</v>
       </c>
       <c r="H118" s="17">
-        <v>0.0070552340982</v>
+        <v>0.0059555716492</v>
       </c>
       <c r="I118" s="16">
-        <v>8.83</v>
+        <v>6.78</v>
       </c>
       <c r="J118" s="11" t="s">
         <v>13</v>
@@ -4658,28 +4808,28 @@
     </row>
     <row r="119" spans="2:10" ht="15" customHeight="1">
       <c r="B119" s="12" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C119" s="13" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="D119" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F119" s="15">
         <v>2000</v>
       </c>
       <c r="G119" s="16">
-        <v>9667.73</v>
+        <v>9670.2</v>
       </c>
       <c r="H119" s="17">
-        <v>0.0069989183079</v>
+        <v>0.0059440894058</v>
       </c>
       <c r="I119" s="16">
-        <v>9.03</v>
+        <v>6.45</v>
       </c>
       <c r="J119" s="11" t="s">
         <v>13</v>
@@ -4687,28 +4837,28 @@
     </row>
     <row r="120" spans="2:10" ht="15" customHeight="1">
       <c r="B120" s="12" t="s">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="C120" s="13" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D120" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F120" s="15">
         <v>2000</v>
       </c>
       <c r="G120" s="16">
-        <v>9629.13</v>
+        <v>9578.11</v>
       </c>
       <c r="H120" s="17">
-        <v>0.006970973977</v>
+        <v>0.0058874834211</v>
       </c>
       <c r="I120" s="16">
-        <v>9.31</v>
+        <v>6.43</v>
       </c>
       <c r="J120" s="11" t="s">
         <v>13</v>
@@ -4716,28 +4866,28 @@
     </row>
     <row r="121" spans="2:10" ht="15" customHeight="1">
       <c r="B121" s="12" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C121" s="13" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="D121" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="F121" s="15">
         <v>2000</v>
       </c>
       <c r="G121" s="16">
-        <v>9489.77</v>
+        <v>9525.65</v>
       </c>
       <c r="H121" s="17">
-        <v>0.006870084807</v>
+        <v>0.0058552372493</v>
       </c>
       <c r="I121" s="16">
-        <v>8.88</v>
+        <v>6.40</v>
       </c>
       <c r="J121" s="11" t="s">
         <v>13</v>
@@ -4745,28 +4895,28 @@
     </row>
     <row r="122" spans="2:10" ht="15" customHeight="1">
       <c r="B122" s="12" t="s">
-        <v>184</v>
+        <v>144</v>
       </c>
       <c r="C122" s="13" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D122" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E122" s="13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F122" s="15">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="G122" s="16">
-        <v>7262.95</v>
+        <v>9516.11</v>
       </c>
       <c r="H122" s="17">
-        <v>0.0052579864895</v>
+        <v>0.0058493731914</v>
       </c>
       <c r="I122" s="16">
-        <v>9.03</v>
+        <v>6.40</v>
       </c>
       <c r="J122" s="11" t="s">
         <v>13</v>
@@ -4774,28 +4924,28 @@
     </row>
     <row r="123" spans="2:10" ht="15" customHeight="1">
       <c r="B123" s="12" t="s">
-        <v>189</v>
+        <v>144</v>
       </c>
       <c r="C123" s="13" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D123" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F123" s="15">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G123" s="16">
-        <v>4922.76</v>
+        <v>9505.01</v>
       </c>
       <c r="H123" s="17">
-        <v>0.003563814369</v>
+        <v>0.0058425502309</v>
       </c>
       <c r="I123" s="16">
-        <v>8.3</v>
+        <v>6.40</v>
       </c>
       <c r="J123" s="11" t="s">
         <v>13</v>
@@ -4803,28 +4953,28 @@
     </row>
     <row r="124" spans="2:10" ht="15" customHeight="1">
       <c r="B124" s="12" t="s">
-        <v>191</v>
+        <v>77</v>
       </c>
       <c r="C124" s="13" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="D124" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F124" s="15">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G124" s="16">
-        <v>4870.99</v>
+        <v>9504.28</v>
       </c>
       <c r="H124" s="17">
-        <v>0.0035263356639</v>
+        <v>0.0058421015137</v>
       </c>
       <c r="I124" s="16">
-        <v>8.26</v>
+        <v>6.41</v>
       </c>
       <c r="J124" s="11" t="s">
         <v>13</v>
@@ -4832,28 +4982,28 @@
     </row>
     <row r="125" spans="2:10" ht="15" customHeight="1">
       <c r="B125" s="12" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="C125" s="13" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="D125" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F125" s="15">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G125" s="16">
-        <v>4851.14</v>
+        <v>9365.16</v>
       </c>
       <c r="H125" s="17">
-        <v>0.003511965328</v>
+        <v>0.0057565870757</v>
       </c>
       <c r="I125" s="16">
-        <v>8.49</v>
+        <v>6.84</v>
       </c>
       <c r="J125" s="11" t="s">
         <v>13</v>
@@ -4861,28 +5011,28 @@
     </row>
     <row r="126" spans="2:10" ht="15" customHeight="1">
       <c r="B126" s="12" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C126" s="13" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="D126" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="F126" s="15">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="G126" s="16">
-        <v>4846.50</v>
+        <v>7152.85</v>
       </c>
       <c r="H126" s="17">
-        <v>0.0035086062167</v>
+        <v>0.0043967218782</v>
       </c>
       <c r="I126" s="16">
-        <v>8.83</v>
+        <v>7.32</v>
       </c>
       <c r="J126" s="11" t="s">
         <v>13</v>
@@ -4890,28 +5040,28 @@
     </row>
     <row r="127" spans="2:10" ht="15" customHeight="1">
       <c r="B127" s="12" t="s">
-        <v>182</v>
+        <v>50</v>
       </c>
       <c r="C127" s="13" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D127" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E127" s="13" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="F127" s="15">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="G127" s="16">
-        <v>4720.12</v>
+        <v>7143.72</v>
       </c>
       <c r="H127" s="17">
-        <v>0.0034171138709</v>
+        <v>0.0043911098395</v>
       </c>
       <c r="I127" s="16">
-        <v>8.87</v>
+        <v>6.43</v>
       </c>
       <c r="J127" s="11" t="s">
         <v>13</v>
@@ -4919,36 +5069,57 @@
     </row>
     <row r="128" spans="2:10" ht="15" customHeight="1">
       <c r="B128" s="12" t="s">
-        <v>13</v>
+        <v>170</v>
+      </c>
+      <c r="C128" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="D128" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E128" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F128" s="15">
+        <v>1000</v>
+      </c>
+      <c r="G128" s="16">
+        <v>4919.62</v>
+      </c>
+      <c r="H128" s="17">
+        <v>0.0030239975515</v>
+      </c>
+      <c r="I128" s="16">
+        <v>6.28</v>
       </c>
       <c r="J128" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="129" spans="2:10" ht="15" customHeight="1">
-      <c r="B129" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="C129" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D129" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E129" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F129" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G129" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="H129" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="I129" s="9" t="s">
-        <v>13</v>
+      <c r="B129" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="C129" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="D129" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E129" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F129" s="15">
+        <v>1000</v>
+      </c>
+      <c r="G129" s="16">
+        <v>4834.27</v>
+      </c>
+      <c r="H129" s="17">
+        <v>0.0029715345175</v>
+      </c>
+      <c r="I129" s="16">
+        <v>6.45</v>
       </c>
       <c r="J129" s="11" t="s">
         <v>13</v>
@@ -4956,36 +5127,57 @@
     </row>
     <row r="130" spans="2:10" ht="15" customHeight="1">
       <c r="B130" s="12" t="s">
-        <v>13</v>
+        <v>179</v>
+      </c>
+      <c r="C130" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="D130" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E130" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F130" s="15">
+        <v>1000</v>
+      </c>
+      <c r="G130" s="16">
+        <v>4829.32</v>
+      </c>
+      <c r="H130" s="17">
+        <v>0.002968491846</v>
+      </c>
+      <c r="I130" s="16">
+        <v>6.45</v>
       </c>
       <c r="J130" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="131" spans="2:10" ht="15" customHeight="1">
-      <c r="B131" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="C131" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D131" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E131" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F131" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G131" s="9">
-        <v>99596.23999999999</v>
-      </c>
-      <c r="H131" s="10">
-        <v>0.0721023391776</v>
-      </c>
-      <c r="I131" s="9" t="s">
-        <v>13</v>
+      <c r="B131" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C131" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="D131" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E131" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F131" s="15">
+        <v>1000</v>
+      </c>
+      <c r="G131" s="16">
+        <v>4793.46</v>
+      </c>
+      <c r="H131" s="17">
+        <v>0.0029464493809</v>
+      </c>
+      <c r="I131" s="16">
+        <v>6.75</v>
       </c>
       <c r="J131" s="11" t="s">
         <v>13</v>
@@ -4993,28 +5185,28 @@
     </row>
     <row r="132" spans="2:10" ht="15" customHeight="1">
       <c r="B132" s="12" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="C132" s="13" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D132" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E132" s="13" t="s">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="F132" s="15">
-        <v>40000000</v>
+        <v>1000</v>
       </c>
       <c r="G132" s="16">
-        <v>39965.16</v>
+        <v>4792.29</v>
       </c>
       <c r="H132" s="17">
-        <v>0.0289326336176</v>
+        <v>0.002945730204</v>
       </c>
       <c r="I132" s="16">
-        <v>6.37</v>
+        <v>6.41</v>
       </c>
       <c r="J132" s="11" t="s">
         <v>13</v>
@@ -5022,28 +5214,28 @@
     </row>
     <row r="133" spans="2:10" ht="15" customHeight="1">
       <c r="B133" s="12" t="s">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="C133" s="13" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D133" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E133" s="13" t="s">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="F133" s="15">
-        <v>40000000</v>
+        <v>800</v>
       </c>
       <c r="G133" s="16">
-        <v>39721.72</v>
+        <v>3932.34</v>
       </c>
       <c r="H133" s="17">
-        <v>0.0287563961065</v>
+        <v>0.0024171351713</v>
       </c>
       <c r="I133" s="16">
-        <v>6.39</v>
+        <v>6.28</v>
       </c>
       <c r="J133" s="11" t="s">
         <v>13</v>
@@ -5051,57 +5243,36 @@
     </row>
     <row r="134" spans="2:10" ht="15" customHeight="1">
       <c r="B134" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="C134" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="D134" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E134" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F134" s="15">
-        <v>10000000</v>
-      </c>
-      <c r="G134" s="16">
-        <v>9978.93</v>
-      </c>
-      <c r="H134" s="17">
-        <v>0.0072242104269</v>
-      </c>
-      <c r="I134" s="16">
-        <v>6.42</v>
+        <v>13</v>
       </c>
       <c r="J134" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="135" spans="2:10" ht="15" customHeight="1">
-      <c r="B135" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="C135" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="D135" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E135" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F135" s="15">
-        <v>10000000</v>
-      </c>
-      <c r="G135" s="16">
-        <v>9930.43</v>
-      </c>
-      <c r="H135" s="17">
-        <v>0.0071890990266</v>
-      </c>
-      <c r="I135" s="16">
-        <v>6.39</v>
+      <c r="B135" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C135" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D135" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E135" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F135" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G135" s="9">
+        <v>244747.15</v>
+      </c>
+      <c r="H135" s="10">
+        <v>0.1504414532707</v>
+      </c>
+      <c r="I135" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J135" s="11" t="s">
         <v>13</v>
@@ -5109,36 +5280,57 @@
     </row>
     <row r="136" spans="2:10" ht="15" customHeight="1">
       <c r="B136" s="12" t="s">
-        <v>13</v>
+        <v>196</v>
+      </c>
+      <c r="C136" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="D136" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E136" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F136" s="15">
+        <v>6000</v>
+      </c>
+      <c r="G136" s="16">
+        <v>29509.05</v>
+      </c>
+      <c r="H136" s="17">
+        <v>0.0181386560238</v>
+      </c>
+      <c r="I136" s="16">
+        <v>6.98</v>
       </c>
       <c r="J136" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="137" spans="2:10" ht="15" customHeight="1">
-      <c r="B137" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="C137" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D137" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E137" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F137" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G137" s="9">
-        <v>3699.46</v>
-      </c>
-      <c r="H137" s="10">
-        <v>0.0026782107406</v>
-      </c>
-      <c r="I137" s="9" t="s">
-        <v>13</v>
+      <c r="B137" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="C137" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="D137" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E137" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F137" s="15">
+        <v>5000</v>
+      </c>
+      <c r="G137" s="16">
+        <v>23849.85</v>
+      </c>
+      <c r="H137" s="17">
+        <v>0.0146600526065</v>
+      </c>
+      <c r="I137" s="16">
+        <v>8.94</v>
       </c>
       <c r="J137" s="11" t="s">
         <v>13</v>
@@ -5146,28 +5338,28 @@
     </row>
     <row r="138" spans="2:10" ht="15" customHeight="1">
       <c r="B138" s="12" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="C138" s="13" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D138" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E138" s="13" t="s">
-        <v>208</v>
+        <v>143</v>
       </c>
       <c r="F138" s="15">
-        <v>33907.017</v>
+        <v>4000</v>
       </c>
       <c r="G138" s="16">
-        <v>3699.46</v>
+        <v>19593.34</v>
       </c>
       <c r="H138" s="17">
-        <v>0.0026782107406</v>
-      </c>
-      <c r="I138" s="16" t="s">
-        <v>13</v>
+        <v>0.0120436562552</v>
+      </c>
+      <c r="I138" s="16">
+        <v>7.36</v>
       </c>
       <c r="J138" s="11" t="s">
         <v>13</v>
@@ -5175,36 +5367,57 @@
     </row>
     <row r="139" spans="2:10" ht="15" customHeight="1">
       <c r="B139" s="12" t="s">
-        <v>13</v>
+        <v>202</v>
+      </c>
+      <c r="C139" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="D139" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E139" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="F139" s="15">
+        <v>4000</v>
+      </c>
+      <c r="G139" s="16">
+        <v>19560.80</v>
+      </c>
+      <c r="H139" s="17">
+        <v>0.0120236545314</v>
+      </c>
+      <c r="I139" s="16">
+        <v>7.07</v>
       </c>
       <c r="J139" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="140" spans="2:10" ht="15" customHeight="1">
-      <c r="B140" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C140" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D140" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E140" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F140" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G140" s="9">
-        <v>67680.97</v>
-      </c>
-      <c r="H140" s="10">
-        <v>0.0489973944279</v>
-      </c>
-      <c r="I140" s="9" t="s">
-        <v>13</v>
+      <c r="B140" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C140" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="D140" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E140" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F140" s="15">
+        <v>4000</v>
+      </c>
+      <c r="G140" s="16">
+        <v>19189.92</v>
+      </c>
+      <c r="H140" s="17">
+        <v>0.0117956815961</v>
+      </c>
+      <c r="I140" s="16">
+        <v>6.42</v>
       </c>
       <c r="J140" s="11" t="s">
         <v>13</v>
@@ -5212,152 +5425,173 @@
     </row>
     <row r="141" spans="2:10" ht="15" customHeight="1">
       <c r="B141" s="12" t="s">
-        <v>13</v>
+        <v>198</v>
+      </c>
+      <c r="C141" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="D141" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E141" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F141" s="15">
+        <v>4000</v>
+      </c>
+      <c r="G141" s="16">
+        <v>19039.86</v>
+      </c>
+      <c r="H141" s="17">
+        <v>0.0117034425466</v>
+      </c>
+      <c r="I141" s="16">
+        <v>8.94</v>
       </c>
       <c r="J141" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="142" spans="2:10" ht="15" customHeight="1">
-      <c r="B142" s="18" t="s">
+      <c r="B142" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="C142" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="D142" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E142" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F142" s="15">
+        <v>3500</v>
+      </c>
+      <c r="G142" s="16">
+        <v>17040.99</v>
+      </c>
+      <c r="H142" s="17">
+        <v>0.0104747748882</v>
+      </c>
+      <c r="I142" s="16">
+        <v>7.51</v>
+      </c>
+      <c r="J142" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="143" spans="2:10" ht="15" customHeight="1">
+      <c r="B143" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="C143" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="D143" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E143" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F143" s="15">
+        <v>2000</v>
+      </c>
+      <c r="G143" s="16">
+        <v>9973.02</v>
+      </c>
+      <c r="H143" s="17">
+        <v>0.0061302271438</v>
+      </c>
+      <c r="I143" s="16">
+        <v>8.23</v>
+      </c>
+      <c r="J143" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="144" spans="2:10" ht="15" customHeight="1">
+      <c r="B144" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="C144" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="C142" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D142" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E142" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F142" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G142" s="19">
-        <v>21683.547200430417</v>
-      </c>
-      <c r="H142" s="20">
-        <v>0.015697725886281096</v>
-      </c>
-      <c r="I142" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J142" s="21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="143" spans="2:10" ht="15" customHeight="1">
-      <c r="B143" s="18" t="s">
+      <c r="D144" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E144" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F144" s="15">
+        <v>2000</v>
+      </c>
+      <c r="G144" s="16">
+        <v>9957.34</v>
+      </c>
+      <c r="H144" s="17">
+        <v>0.0061205889438</v>
+      </c>
+      <c r="I144" s="16">
+        <v>8.23</v>
+      </c>
+      <c r="J144" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="145" spans="2:10" ht="15" customHeight="1">
+      <c r="B145" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="C145" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="C143" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D143" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E143" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F143" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G143" s="19">
-        <v>1381317.73720043</v>
-      </c>
-      <c r="H143" s="20">
-        <v>0.9999999999949811</v>
-      </c>
-      <c r="I143" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J143" s="21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="144" spans="2:10" ht="15" customHeight="1">
-      <c r="B144" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C144" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D144" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E144" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F144" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G144" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="H144" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="I144" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J144" s="21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="145" spans="2:10" ht="15" customHeight="1">
-      <c r="B145" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="C145" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D145" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E145" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F145" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G145" s="19">
-        <v>-180000</v>
-      </c>
-      <c r="H145" s="20">
-        <v>-0.13031035159572546</v>
-      </c>
-      <c r="I145" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J145" s="21" t="s">
+      <c r="D145" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E145" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F145" s="15">
+        <v>2000</v>
+      </c>
+      <c r="G145" s="16">
+        <v>9931.97</v>
+      </c>
+      <c r="H145" s="17">
+        <v>0.0061049944837</v>
+      </c>
+      <c r="I145" s="16">
+        <v>8.06</v>
+      </c>
+      <c r="J145" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="146" spans="2:10" ht="15" customHeight="1">
       <c r="B146" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="C146" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="C146" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D146" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E146" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F146" s="8" t="s">
-        <v>13</v>
+      <c r="D146" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E146" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="F146" s="15">
+        <v>2000</v>
       </c>
       <c r="G146" s="16">
-        <v>-20000</v>
+        <v>9802.73</v>
       </c>
       <c r="H146" s="17">
-        <v>-0.014478927955080613</v>
-      </c>
-      <c r="I146" s="8" t="s">
-        <v>13</v>
+        <v>0.0060255530952</v>
+      </c>
+      <c r="I146" s="16">
+        <v>7.27</v>
       </c>
       <c r="J146" s="11" t="s">
         <v>13</v>
@@ -5367,26 +5601,26 @@
       <c r="B147" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="C147" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D147" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E147" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F147" s="8" t="s">
-        <v>13</v>
+      <c r="C147" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="D147" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E147" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="F147" s="15">
+        <v>2000</v>
       </c>
       <c r="G147" s="16">
-        <v>-10000</v>
+        <v>9332.05</v>
       </c>
       <c r="H147" s="17">
-        <v>-0.007239463977540306</v>
-      </c>
-      <c r="I147" s="8" t="s">
-        <v>13</v>
+        <v>0.0057362349837</v>
+      </c>
+      <c r="I147" s="16">
+        <v>7.38</v>
       </c>
       <c r="J147" s="11" t="s">
         <v>13</v>
@@ -5394,28 +5628,28 @@
     </row>
     <row r="148" spans="2:10" ht="15" customHeight="1">
       <c r="B148" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="C148" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D148" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E148" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F148" s="8" t="s">
-        <v>13</v>
+        <v>216</v>
+      </c>
+      <c r="C148" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="D148" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E148" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F148" s="15">
+        <v>1500</v>
       </c>
       <c r="G148" s="16">
-        <v>-10000</v>
+        <v>7109.95</v>
       </c>
       <c r="H148" s="17">
-        <v>-0.007239463977540306</v>
-      </c>
-      <c r="I148" s="8" t="s">
-        <v>13</v>
+        <v>0.0043703520579</v>
+      </c>
+      <c r="I148" s="16">
+        <v>8.14</v>
       </c>
       <c r="J148" s="11" t="s">
         <v>13</v>
@@ -5425,26 +5659,26 @@
       <c r="B149" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="C149" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D149" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E149" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F149" s="8" t="s">
-        <v>13</v>
+      <c r="C149" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="D149" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E149" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F149" s="15">
+        <v>1500</v>
       </c>
       <c r="G149" s="16">
-        <v>-10000</v>
+        <v>7078.52</v>
       </c>
       <c r="H149" s="17">
-        <v>-0.007239463977540306</v>
-      </c>
-      <c r="I149" s="8" t="s">
-        <v>13</v>
+        <v>0.0043510326302</v>
+      </c>
+      <c r="I149" s="16">
+        <v>8.14</v>
       </c>
       <c r="J149" s="11" t="s">
         <v>13</v>
@@ -5452,28 +5686,28 @@
     </row>
     <row r="150" spans="2:10" ht="15" customHeight="1">
       <c r="B150" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="C150" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D150" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E150" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F150" s="8" t="s">
-        <v>13</v>
+        <v>212</v>
+      </c>
+      <c r="C150" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="D150" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E150" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="F150" s="15">
+        <v>1000</v>
       </c>
       <c r="G150" s="16">
-        <v>-5000</v>
+        <v>4989.22</v>
       </c>
       <c r="H150" s="17">
-        <v>-0.003619731988770153</v>
-      </c>
-      <c r="I150" s="8" t="s">
-        <v>13</v>
+        <v>0.0030667793577</v>
+      </c>
+      <c r="I150" s="16">
+        <v>7.17</v>
       </c>
       <c r="J150" s="11" t="s">
         <v>13</v>
@@ -5481,28 +5715,28 @@
     </row>
     <row r="151" spans="2:10" ht="15" customHeight="1">
       <c r="B151" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="C151" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D151" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E151" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F151" s="8" t="s">
-        <v>13</v>
+        <v>220</v>
+      </c>
+      <c r="C151" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="D151" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E151" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F151" s="15">
+        <v>1000</v>
       </c>
       <c r="G151" s="16">
-        <v>-5000</v>
+        <v>4988.16</v>
       </c>
       <c r="H151" s="17">
-        <v>-0.003619731988770153</v>
-      </c>
-      <c r="I151" s="8" t="s">
-        <v>13</v>
+        <v>0.0030661277957</v>
+      </c>
+      <c r="I151" s="16">
+        <v>7.22</v>
       </c>
       <c r="J151" s="11" t="s">
         <v>13</v>
@@ -5510,28 +5744,28 @@
     </row>
     <row r="152" spans="2:10" ht="15" customHeight="1">
       <c r="B152" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="C152" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D152" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E152" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F152" s="8" t="s">
-        <v>13</v>
+        <v>212</v>
+      </c>
+      <c r="C152" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="D152" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E152" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="F152" s="15">
+        <v>1000</v>
       </c>
       <c r="G152" s="16">
-        <v>-10000</v>
+        <v>4874</v>
       </c>
       <c r="H152" s="17">
-        <v>-0.007239463977540306</v>
-      </c>
-      <c r="I152" s="8" t="s">
-        <v>13</v>
+        <v>0.0029959557986</v>
+      </c>
+      <c r="I152" s="16">
+        <v>7.61</v>
       </c>
       <c r="J152" s="11" t="s">
         <v>13</v>
@@ -5539,28 +5773,28 @@
     </row>
     <row r="153" spans="2:10" ht="15" customHeight="1">
       <c r="B153" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="C153" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D153" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E153" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F153" s="8" t="s">
-        <v>13</v>
+        <v>223</v>
+      </c>
+      <c r="C153" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="D153" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E153" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F153" s="15">
+        <v>1000</v>
       </c>
       <c r="G153" s="16">
-        <v>-20000</v>
+        <v>4794.48</v>
       </c>
       <c r="H153" s="17">
-        <v>-0.014478927955080613</v>
-      </c>
-      <c r="I153" s="8" t="s">
-        <v>13</v>
+        <v>0.0029470763556</v>
+      </c>
+      <c r="I153" s="16">
+        <v>8.07</v>
       </c>
       <c r="J153" s="11" t="s">
         <v>13</v>
@@ -5568,28 +5802,28 @@
     </row>
     <row r="154" spans="2:10" ht="15" customHeight="1">
       <c r="B154" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="C154" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D154" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E154" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F154" s="8" t="s">
-        <v>13</v>
+        <v>214</v>
+      </c>
+      <c r="C154" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="D154" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E154" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="F154" s="15">
+        <v>1000</v>
       </c>
       <c r="G154" s="16">
-        <v>-10000</v>
+        <v>4747.45</v>
       </c>
       <c r="H154" s="17">
-        <v>-0.007239463977540306</v>
-      </c>
-      <c r="I154" s="8" t="s">
-        <v>13</v>
+        <v>0.0029181679024</v>
+      </c>
+      <c r="I154" s="16">
+        <v>7.17</v>
       </c>
       <c r="J154" s="11" t="s">
         <v>13</v>
@@ -5597,28 +5831,28 @@
     </row>
     <row r="155" spans="2:10" ht="15" customHeight="1">
       <c r="B155" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="C155" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D155" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E155" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F155" s="8" t="s">
-        <v>13</v>
+        <v>226</v>
+      </c>
+      <c r="C155" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="D155" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E155" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F155" s="15">
+        <v>1000</v>
       </c>
       <c r="G155" s="16">
-        <v>-10000</v>
+        <v>4724.34</v>
       </c>
       <c r="H155" s="17">
-        <v>-0.007239463977540306</v>
-      </c>
-      <c r="I155" s="8" t="s">
-        <v>13</v>
+        <v>0.0029039626216</v>
+      </c>
+      <c r="I155" s="16">
+        <v>9.18</v>
       </c>
       <c r="J155" s="11" t="s">
         <v>13</v>
@@ -5626,28 +5860,28 @@
     </row>
     <row r="156" spans="2:10" ht="15" customHeight="1">
       <c r="B156" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="C156" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D156" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E156" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F156" s="8" t="s">
-        <v>13</v>
+        <v>226</v>
+      </c>
+      <c r="C156" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="D156" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E156" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F156" s="15">
+        <v>1000</v>
       </c>
       <c r="G156" s="16">
-        <v>-15000</v>
+        <v>4660.11</v>
       </c>
       <c r="H156" s="17">
-        <v>-0.010859195966310459</v>
-      </c>
-      <c r="I156" s="8" t="s">
-        <v>13</v>
+        <v>0.002864481653</v>
+      </c>
+      <c r="I156" s="16">
+        <v>9.18</v>
       </c>
       <c r="J156" s="11" t="s">
         <v>13</v>
@@ -5655,27 +5889,6 @@
     </row>
     <row r="157" spans="2:10" ht="15" customHeight="1">
       <c r="B157" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="C157" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D157" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E157" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F157" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G157" s="16">
-        <v>-10000</v>
-      </c>
-      <c r="H157" s="17">
-        <v>-0.007239463977540306</v>
-      </c>
-      <c r="I157" s="8" t="s">
         <v>13</v>
       </c>
       <c r="J157" s="11" t="s">
@@ -5683,28 +5896,28 @@
       </c>
     </row>
     <row r="158" spans="2:10" ht="15" customHeight="1">
-      <c r="B158" s="12" t="s">
-        <v>224</v>
+      <c r="B158" s="7" t="s">
+        <v>229</v>
       </c>
       <c r="C158" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D158" s="8" t="s">
+      <c r="D158" s="9" t="s">
         <v>13</v>
       </c>
       <c r="E158" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F158" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G158" s="16">
-        <v>-10000</v>
-      </c>
-      <c r="H158" s="17">
-        <v>-0.007239463977540306</v>
-      </c>
-      <c r="I158" s="8" t="s">
+      <c r="F158" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G158" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="H158" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="I158" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J158" s="11" t="s">
@@ -5713,27 +5926,6 @@
     </row>
     <row r="159" spans="2:10" ht="15" customHeight="1">
       <c r="B159" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="C159" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D159" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E159" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F159" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G159" s="16">
-        <v>-10000</v>
-      </c>
-      <c r="H159" s="17">
-        <v>-0.007239463977540306</v>
-      </c>
-      <c r="I159" s="8" t="s">
         <v>13</v>
       </c>
       <c r="J159" s="11" t="s">
@@ -5741,28 +5933,28 @@
       </c>
     </row>
     <row r="160" spans="2:10" ht="15" customHeight="1">
-      <c r="B160" s="12" t="s">
-        <v>226</v>
+      <c r="B160" s="7" t="s">
+        <v>230</v>
       </c>
       <c r="C160" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D160" s="8" t="s">
+      <c r="D160" s="9" t="s">
         <v>13</v>
       </c>
       <c r="E160" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F160" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G160" s="16">
-        <v>-5000</v>
-      </c>
-      <c r="H160" s="17">
-        <v>-0.003619731988770153</v>
-      </c>
-      <c r="I160" s="8" t="s">
+      <c r="F160" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G160" s="9">
+        <v>66439.9</v>
+      </c>
+      <c r="H160" s="10">
+        <v>0.0408393524141</v>
+      </c>
+      <c r="I160" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J160" s="11" t="s">
@@ -5771,28 +5963,28 @@
     </row>
     <row r="161" spans="2:10" ht="15" customHeight="1">
       <c r="B161" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="C161" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D161" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E161" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F161" s="8" t="s">
-        <v>13</v>
+        <v>231</v>
+      </c>
+      <c r="C161" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D161" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E161" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F161" s="15">
+        <v>50000000</v>
       </c>
       <c r="G161" s="16">
-        <v>-10000</v>
+        <v>49228.25</v>
       </c>
       <c r="H161" s="17">
-        <v>-0.007239463977540306</v>
-      </c>
-      <c r="I161" s="8" t="s">
-        <v>13</v>
+        <v>0.0302596760453</v>
+      </c>
+      <c r="I161" s="16">
+        <v>5.61</v>
       </c>
       <c r="J161" s="11" t="s">
         <v>13</v>
@@ -5800,178 +5992,1386 @@
     </row>
     <row r="162" spans="2:10" ht="15" customHeight="1">
       <c r="B162" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="C162" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D162" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E162" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F162" s="8" t="s">
-        <v>13</v>
+        <v>231</v>
+      </c>
+      <c r="C162" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="D162" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E162" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F162" s="15">
+        <v>17500000</v>
       </c>
       <c r="G162" s="16">
+        <v>17211.65</v>
+      </c>
+      <c r="H162" s="17">
+        <v>0.0105796763688</v>
+      </c>
+      <c r="I162" s="16">
+        <v>5.61</v>
+      </c>
+      <c r="J162" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="163" spans="2:10" ht="15" customHeight="1">
+      <c r="B163" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J163" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="164" spans="2:10" ht="15" customHeight="1">
+      <c r="B164" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C164" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D164" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E164" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F164" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G164" s="9">
+        <v>3794.52</v>
+      </c>
+      <c r="H164" s="10">
+        <v>0.0023324198188</v>
+      </c>
+      <c r="I164" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J164" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="165" spans="2:10" ht="15" customHeight="1">
+      <c r="B165" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="C165" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="D165" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E165" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="F165" s="15">
+        <v>33907.017</v>
+      </c>
+      <c r="G165" s="16">
+        <v>3794.52</v>
+      </c>
+      <c r="H165" s="17">
+        <v>0.0023324198188</v>
+      </c>
+      <c r="I165" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J165" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="166" spans="2:10" ht="15" customHeight="1">
+      <c r="B166" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J166" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="167" spans="2:10" ht="15" customHeight="1">
+      <c r="B167" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="C167" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D167" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E167" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F167" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G167" s="9">
+        <v>20468.72</v>
+      </c>
+      <c r="H167" s="10">
+        <v>0.0125817358176</v>
+      </c>
+      <c r="I167" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J167" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="168" spans="2:10" ht="15" customHeight="1">
+      <c r="B168" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J168" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="169" spans="2:10" ht="15" customHeight="1">
+      <c r="B169" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="C169" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D169" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E169" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F169" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G169" s="19">
+        <v>24393.032841290347</v>
+      </c>
+      <c r="H169" s="20">
+        <v>0.0149939368460435</v>
+      </c>
+      <c r="I169" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J169" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="170" spans="2:10" ht="15" customHeight="1">
+      <c r="B170" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="C170" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D170" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E170" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F170" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G170" s="19">
+        <v>1626859.78284129</v>
+      </c>
+      <c r="H170" s="20">
+        <v>0.9999999999935435</v>
+      </c>
+      <c r="I170" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J170" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="171" spans="2:10" ht="15" customHeight="1">
+      <c r="B171" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C171" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D171" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E171" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F171" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G171" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H171" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="I171" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J171" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="172" spans="2:10" ht="15" customHeight="1">
+      <c r="B172" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="C172" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D172" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E172" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F172" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G172" s="19">
+        <v>-332500</v>
+      </c>
+      <c r="H172" s="20">
+        <v>-0.20438147374895016</v>
+      </c>
+      <c r="I172" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J172" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="173" spans="2:10" ht="15" customHeight="1">
+      <c r="B173" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="C173" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D173" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E173" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F173" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G173" s="16">
+        <v>-15000</v>
+      </c>
+      <c r="H173" s="17">
+        <v>-0.009220216860854898</v>
+      </c>
+      <c r="I173" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J173" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="174" spans="2:10" ht="15" customHeight="1">
+      <c r="B174" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C174" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D174" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E174" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F174" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G174" s="16">
         <v>-10000</v>
       </c>
-      <c r="H162" s="17">
-        <v>-0.007239463977540306</v>
-      </c>
-      <c r="I162" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J162" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="163" spans="2:10" ht="15" customHeight="1">
-      <c r="B163" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C163" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="D163" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="E163" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F163" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G163" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="H163" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="I163" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="J163" s="22" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="166" spans="2:9" ht="15" customHeight="1">
-      <c r="B166" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="C166" s="23"/>
-      <c r="D166" s="23"/>
-      <c r="E166" s="23"/>
-      <c r="F166" s="23"/>
-      <c r="G166" s="23"/>
-      <c r="H166" s="23"/>
-      <c r="I166" s="23"/>
-    </row>
-    <row r="167" spans="2:8" ht="15" customHeight="1">
-      <c r="B167" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="C167" s="23"/>
-      <c r="D167" s="23"/>
-      <c r="E167" s="23"/>
-      <c r="F167" s="23"/>
-      <c r="G167" s="23"/>
-      <c r="H167" s="23"/>
-    </row>
-    <row r="168" spans="2:8" ht="15" customHeight="1">
-      <c r="B168" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="C168" s="23"/>
-      <c r="D168" s="23"/>
-      <c r="E168" s="23"/>
-      <c r="F168" s="23"/>
-      <c r="G168" s="23"/>
-      <c r="H168" s="23"/>
-    </row>
-    <row r="169" spans="2:8" ht="15" customHeight="1">
-      <c r="B169" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="C169" s="23"/>
-      <c r="D169" s="23"/>
-      <c r="E169" s="23"/>
-      <c r="F169" s="23"/>
-      <c r="G169" s="23"/>
-      <c r="H169" s="23"/>
-    </row>
-    <row r="170" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B170" s="24" t="s">
-        <v>233</v>
-      </c>
-      <c r="C170" s="23"/>
-      <c r="D170" s="23"/>
-      <c r="E170" s="23"/>
-      <c r="F170" s="23"/>
-      <c r="G170" s="23"/>
-      <c r="H170" s="23"/>
-    </row>
-    <row r="171" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B171" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="C171" s="23"/>
-      <c r="D171" s="23"/>
-      <c r="E171" s="23"/>
-      <c r="F171" s="23"/>
-      <c r="G171" s="23"/>
-      <c r="H171" s="23"/>
-    </row>
-    <row r="172" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B172" s="24" t="s">
-        <v>235</v>
-      </c>
-      <c r="C172" s="23"/>
-      <c r="D172" s="23"/>
-      <c r="E172" s="23"/>
-      <c r="F172" s="23"/>
-      <c r="G172" s="23"/>
-      <c r="H172" s="23"/>
-    </row>
-    <row r="173" spans="2:7" ht="52.5" customHeight="1">
-      <c r="B173" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="C173" s="25"/>
-      <c r="D173" s="25"/>
-      <c r="E173" s="25"/>
-      <c r="F173" s="25"/>
-      <c r="G173" s="25"/>
-    </row>
-    <row r="176" ht="15">
-      <c r="B176" s="23" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="191" ht="15">
-      <c r="B191" s="23" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="192" ht="15">
-      <c r="B192" s="23" t="s">
-        <v>239</v>
+      <c r="H174" s="17">
+        <v>-0.006146811240569932</v>
+      </c>
+      <c r="I174" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J174" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="175" spans="2:10" ht="15" customHeight="1">
+      <c r="B175" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="C175" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D175" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E175" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F175" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G175" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H175" s="17">
+        <v>-0.006146811240569932</v>
+      </c>
+      <c r="I175" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J175" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="176" spans="2:10" ht="15" customHeight="1">
+      <c r="B176" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="C176" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D176" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E176" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F176" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G176" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H176" s="17">
+        <v>-0.006146811240569932</v>
+      </c>
+      <c r="I176" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J176" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="177" spans="2:10" ht="15" customHeight="1">
+      <c r="B177" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="C177" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D177" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E177" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F177" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G177" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H177" s="17">
+        <v>-0.006146811240569932</v>
+      </c>
+      <c r="I177" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J177" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="178" spans="2:10" ht="15" customHeight="1">
+      <c r="B178" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="C178" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D178" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E178" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F178" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G178" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H178" s="17">
+        <v>-0.003073405620284966</v>
+      </c>
+      <c r="I178" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J178" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="179" spans="2:10" ht="15" customHeight="1">
+      <c r="B179" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="C179" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D179" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E179" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F179" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G179" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H179" s="17">
+        <v>-0.006146811240569932</v>
+      </c>
+      <c r="I179" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J179" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="180" spans="2:10" ht="15" customHeight="1">
+      <c r="B180" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C180" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D180" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E180" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F180" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G180" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H180" s="17">
+        <v>-0.006146811240569932</v>
+      </c>
+      <c r="I180" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J180" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="181" spans="2:10" ht="15" customHeight="1">
+      <c r="B181" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="C181" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D181" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E181" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F181" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G181" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H181" s="17">
+        <v>-0.003073405620284966</v>
+      </c>
+      <c r="I181" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J181" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="182" spans="2:10" ht="15" customHeight="1">
+      <c r="B182" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="C182" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D182" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E182" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F182" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G182" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H182" s="17">
+        <v>-0.006146811240569932</v>
+      </c>
+      <c r="I182" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J182" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="183" spans="2:10" ht="15" customHeight="1">
+      <c r="B183" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="C183" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D183" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E183" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F183" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G183" s="16">
+        <v>-20000</v>
+      </c>
+      <c r="H183" s="17">
+        <v>-0.012293622481139865</v>
+      </c>
+      <c r="I183" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J183" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="184" spans="2:10" ht="15" customHeight="1">
+      <c r="B184" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="C184" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D184" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E184" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F184" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G184" s="16">
+        <v>-20000</v>
+      </c>
+      <c r="H184" s="17">
+        <v>-0.012293622481139865</v>
+      </c>
+      <c r="I184" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J184" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="185" spans="2:10" ht="15" customHeight="1">
+      <c r="B185" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="C185" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D185" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E185" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F185" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G185" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H185" s="17">
+        <v>-0.006146811240569932</v>
+      </c>
+      <c r="I185" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J185" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="186" spans="2:10" ht="15" customHeight="1">
+      <c r="B186" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C186" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D186" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E186" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F186" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G186" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H186" s="17">
+        <v>-0.006146811240569932</v>
+      </c>
+      <c r="I186" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J186" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="187" spans="2:10" ht="15" customHeight="1">
+      <c r="B187" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C187" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D187" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E187" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F187" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G187" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H187" s="17">
+        <v>-0.006146811240569932</v>
+      </c>
+      <c r="I187" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J187" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="188" spans="2:10" ht="15" customHeight="1">
+      <c r="B188" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="C188" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D188" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E188" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F188" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G188" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H188" s="17">
+        <v>-0.006146811240569932</v>
+      </c>
+      <c r="I188" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J188" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="189" spans="2:10" ht="15" customHeight="1">
+      <c r="B189" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="C189" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D189" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E189" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F189" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G189" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H189" s="17">
+        <v>-0.006146811240569932</v>
+      </c>
+      <c r="I189" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J189" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="190" spans="2:10" ht="15" customHeight="1">
+      <c r="B190" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="C190" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D190" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E190" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F190" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G190" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H190" s="17">
+        <v>-0.006146811240569932</v>
+      </c>
+      <c r="I190" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J190" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="191" spans="2:10" ht="15" customHeight="1">
+      <c r="B191" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="C191" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D191" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E191" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F191" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G191" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H191" s="17">
+        <v>-0.006146811240569932</v>
+      </c>
+      <c r="I191" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J191" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="192" spans="2:10" ht="15" customHeight="1">
+      <c r="B192" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C192" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D192" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E192" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F192" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G192" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H192" s="17">
+        <v>-0.006146811240569932</v>
+      </c>
+      <c r="I192" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J192" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="193" spans="2:10" ht="15" customHeight="1">
+      <c r="B193" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C193" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D193" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E193" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F193" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G193" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H193" s="17">
+        <v>-0.003073405620284966</v>
+      </c>
+      <c r="I193" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J193" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="194" spans="2:10" ht="15" customHeight="1">
+      <c r="B194" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C194" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D194" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E194" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F194" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G194" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H194" s="17">
+        <v>-0.003073405620284966</v>
+      </c>
+      <c r="I194" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J194" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="195" spans="2:10" ht="15" customHeight="1">
+      <c r="B195" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="C195" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D195" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E195" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F195" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G195" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H195" s="17">
+        <v>-0.006146811240569932</v>
+      </c>
+      <c r="I195" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J195" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="196" spans="2:10" ht="15" customHeight="1">
+      <c r="B196" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="C196" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D196" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E196" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F196" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G196" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H196" s="17">
+        <v>-0.006146811240569932</v>
+      </c>
+      <c r="I196" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J196" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="197" spans="2:10" ht="15" customHeight="1">
+      <c r="B197" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="C197" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D197" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E197" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F197" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G197" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H197" s="17">
+        <v>-0.003073405620284966</v>
+      </c>
+      <c r="I197" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J197" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="198" spans="2:10" ht="15" customHeight="1">
+      <c r="B198" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C198" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D198" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E198" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F198" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G198" s="16">
+        <v>-7500</v>
+      </c>
+      <c r="H198" s="17">
+        <v>-0.004610108430427449</v>
+      </c>
+      <c r="I198" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J198" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="199" spans="2:10" ht="15" customHeight="1">
+      <c r="B199" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C199" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D199" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E199" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F199" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G199" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H199" s="17">
+        <v>-0.003073405620284966</v>
+      </c>
+      <c r="I199" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J199" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="200" spans="2:10" ht="15" customHeight="1">
+      <c r="B200" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="C200" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D200" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E200" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F200" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G200" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H200" s="17">
+        <v>-0.006146811240569932</v>
+      </c>
+      <c r="I200" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J200" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="201" spans="2:10" ht="15" customHeight="1">
+      <c r="B201" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="C201" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D201" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E201" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F201" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G201" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H201" s="17">
+        <v>-0.006146811240569932</v>
+      </c>
+      <c r="I201" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J201" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="202" spans="2:10" ht="15" customHeight="1">
+      <c r="B202" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="C202" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D202" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E202" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F202" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G202" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H202" s="17">
+        <v>-0.003073405620284966</v>
+      </c>
+      <c r="I202" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J202" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="203" spans="2:10" ht="15" customHeight="1">
+      <c r="B203" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="C203" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D203" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E203" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F203" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G203" s="16">
+        <v>-20000</v>
+      </c>
+      <c r="H203" s="17">
+        <v>-0.012293622481139865</v>
+      </c>
+      <c r="I203" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J203" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="204" spans="2:10" ht="15" customHeight="1">
+      <c r="B204" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="C204" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D204" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E204" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F204" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G204" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H204" s="17">
+        <v>-0.006146811240569932</v>
+      </c>
+      <c r="I204" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J204" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="205" spans="2:10" ht="15" customHeight="1">
+      <c r="B205" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="C205" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D205" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E205" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F205" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G205" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H205" s="17">
+        <v>-0.006146811240569932</v>
+      </c>
+      <c r="I205" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J205" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="206" spans="2:10" ht="15" customHeight="1">
+      <c r="B206" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="C206" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D206" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E206" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F206" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G206" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H206" s="17">
+        <v>-0.003073405620284966</v>
+      </c>
+      <c r="I206" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J206" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="207" spans="2:10" ht="15" customHeight="1">
+      <c r="B207" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C207" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D207" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E207" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F207" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="G207" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H207" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I207" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="J207" s="22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="210" spans="2:9" ht="15" customHeight="1">
+      <c r="B210" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="C210" s="23"/>
+      <c r="D210" s="23"/>
+      <c r="E210" s="23"/>
+      <c r="F210" s="23"/>
+      <c r="G210" s="23"/>
+      <c r="H210" s="23"/>
+      <c r="I210" s="23"/>
+    </row>
+    <row r="211" spans="2:8" ht="15" customHeight="1">
+      <c r="B211" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="C211" s="23"/>
+      <c r="D211" s="23"/>
+      <c r="E211" s="23"/>
+      <c r="F211" s="23"/>
+      <c r="G211" s="23"/>
+      <c r="H211" s="23"/>
+    </row>
+    <row r="212" spans="2:8" ht="15" customHeight="1">
+      <c r="B212" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="C212" s="23"/>
+      <c r="D212" s="23"/>
+      <c r="E212" s="23"/>
+      <c r="F212" s="23"/>
+      <c r="G212" s="23"/>
+      <c r="H212" s="23"/>
+    </row>
+    <row r="213" spans="2:8" ht="15" customHeight="1">
+      <c r="B213" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="C213" s="23"/>
+      <c r="D213" s="23"/>
+      <c r="E213" s="23"/>
+      <c r="F213" s="23"/>
+      <c r="G213" s="23"/>
+      <c r="H213" s="23"/>
+    </row>
+    <row r="214" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B214" s="24" t="s">
+        <v>277</v>
+      </c>
+      <c r="C214" s="23"/>
+      <c r="D214" s="23"/>
+      <c r="E214" s="23"/>
+      <c r="F214" s="23"/>
+      <c r="G214" s="23"/>
+      <c r="H214" s="23"/>
+    </row>
+    <row r="215" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B215" s="24" t="s">
+        <v>278</v>
+      </c>
+      <c r="C215" s="23"/>
+      <c r="D215" s="23"/>
+      <c r="E215" s="23"/>
+      <c r="F215" s="23"/>
+      <c r="G215" s="23"/>
+      <c r="H215" s="23"/>
+    </row>
+    <row r="216" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B216" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="C216" s="23"/>
+      <c r="D216" s="23"/>
+      <c r="E216" s="23"/>
+      <c r="F216" s="23"/>
+      <c r="G216" s="23"/>
+      <c r="H216" s="23"/>
+    </row>
+    <row r="217" spans="2:7" ht="53.25" customHeight="1">
+      <c r="B217" s="25" t="s">
+        <v>280</v>
+      </c>
+      <c r="C217" s="25"/>
+      <c r="D217" s="25"/>
+      <c r="E217" s="25"/>
+      <c r="F217" s="25"/>
+      <c r="G217" s="25"/>
+    </row>
+    <row r="220" ht="15">
+      <c r="B220" s="23" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="235" ht="15">
+      <c r="B235" s="23" t="s">
+        <v>282</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B173:G173"/>
-    <mergeCell ref="B168:H168"/>
-    <mergeCell ref="B169:H169"/>
-    <mergeCell ref="B170:H170"/>
-    <mergeCell ref="B171:H171"/>
-    <mergeCell ref="B172:H172"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B166:I166"/>
-    <mergeCell ref="B167:H167"/>
+    <mergeCell ref="B210:I210"/>
+    <mergeCell ref="B211:H211"/>
+    <mergeCell ref="B217:G217"/>
+    <mergeCell ref="B212:H212"/>
+    <mergeCell ref="B213:H213"/>
+    <mergeCell ref="B214:H214"/>
+    <mergeCell ref="B215:H215"/>
+    <mergeCell ref="B216:H216"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
